--- a/AnalisisFinanciero/data/890903939_2024-12-31_Notas_Activos_intangibles_distintos_de_la_plusvalia_traduccion.xlsx
+++ b/AnalisisFinanciero/data/890903939_2024-12-31_Notas_Activos_intangibles_distintos_de_la_plusvalia_traduccion.xlsx
@@ -1,12 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E82AEB8-864A-4B0C-A8D0-359B29961C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -121,46 +146,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <family val="2"/>
     </font>
     <font>
-      <color theme="1"/>
-      <sz val="9"/>
       <name val="Helvetica Neue"/>
-    </font>
-    <font/>
-    <font>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
       <b/>
-      <color theme="1"/>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10.00"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,26 +200,264 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="24">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -206,19 +474,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FF000000"/>
-      </right>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -232,9 +513,18 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
-      </top>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -265,14 +555,25 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -284,90 +585,143 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf borderId="4" applyBorder="1"/>
+    <xf fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="9" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" applyBorder="1"/>
+    <xf fontId="3" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="12" applyFill="1" borderId="13" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="4" applyFont="1" fillId="13" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="14" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="15" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="5" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="16" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="17" applyFill="1" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf borderId="21" applyBorder="1"/>
+    <xf fontId="6" applyFont="1" borderId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
+    <xf xfId="17" quotePrefix="0" pivotButton="0" fontId="5" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="10" quotePrefix="0" pivotButton="0" borderId="10" applyBorder="1"/>
+    <xf xfId="22" quotePrefix="0" pivotButton="0" borderId="21" applyBorder="1"/>
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="9" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="13" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="12" applyFill="1" borderId="13" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="23" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" borderId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="21" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="24" quotePrefix="0" pivotButton="0" borderId="23" applyBorder="1"/>
+    <xf xfId="4" quotePrefix="0" pivotButton="0" borderId="4" applyBorder="1"/>
+    <xf xfId="18" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="16" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="15" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="14" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="16" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="15" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="12" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="14" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="13" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="20" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="17" applyFill="1" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="11" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="19" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -383,56 +737,116 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -470,15 +884,15 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
@@ -539,32 +953,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
+            <a:satMod val="170000"/>
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:satMod val="120000"/>
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -573,21 +987,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.00" customHeight="1" defaultColWidth="14.47"/>
   <cols>
-    <col min="1" max="3" width="3.43" customWidth="1"/>
-    <col min="4" max="4" width="63" customWidth="1"/>
-    <col min="5" max="14" width="18.86" customWidth="1"/>
-    <col min="15" max="26" width="11.57" customWidth="1"/>
+    <col min="1" max="3" width="3.43" customWidth="1" hidden="0"/>
+    <col min="4" max="4" width="63.04" customWidth="1" hidden="0"/>
+    <col min="5" max="14" width="18.89" customWidth="1" hidden="0"/>
+    <col min="15" max="26" width="11.53" customWidth="1" hidden="0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="12.75" customHeight="true">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -605,7 +1027,7 @@
       <c r="M1" s="3"/>
       <c r="N1" s="4"/>
     </row>
-    <row r="2" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" ht="12.75" customHeight="true">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -639,7 +1061,7 @@
       </c>
       <c r="N2" s="7"/>
     </row>
-    <row r="3" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="12.75" customHeight="true">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -657,7 +1079,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
     </row>
-    <row r="4" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="12.75" customHeight="true">
       <c r="A4" s="10"/>
       <c r="B4" s="11" t="s">
         <v>11</v>
@@ -681,7 +1103,7 @@
       </c>
       <c r="N4" s="14"/>
     </row>
-    <row r="5" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" ht="12.75" customHeight="true">
       <c r="A5" s="10"/>
       <c r="B5" s="15" t="s">
         <v>14</v>
@@ -705,7 +1127,7 @@
       </c>
       <c r="N5" s="9"/>
     </row>
-    <row r="6" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="12.75" customHeight="true">
       <c r="A6" s="10"/>
       <c r="B6" s="16" t="s">
         <v>16</v>
@@ -723,7 +1145,7 @@
       <c r="M6" s="14"/>
       <c r="N6" s="14"/>
     </row>
-    <row r="7" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="12.75" customHeight="true">
       <c r="A7" s="10"/>
       <c r="B7" s="17"/>
       <c r="C7" s="15" t="s">
@@ -751,7 +1173,7 @@
         <v>82017292</v>
       </c>
     </row>
-    <row r="8" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="21.75" customHeight="true">
       <c r="A8" s="10"/>
       <c r="B8" s="17"/>
       <c r="C8" s="11" t="s">
@@ -775,7 +1197,7 @@
         <v>20205487</v>
       </c>
     </row>
-    <row r="9" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="21.75" customHeight="true">
       <c r="A9" s="10"/>
       <c r="B9" s="17"/>
       <c r="C9" s="15" t="s">
@@ -793,7 +1215,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
     </row>
-    <row r="10" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="12.75" customHeight="true">
       <c r="A10" s="10"/>
       <c r="B10" s="17"/>
       <c r="C10" s="11" t="s">
@@ -817,7 +1239,7 @@
         <v>7395247</v>
       </c>
     </row>
-    <row r="11" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="21.75" customHeight="true">
       <c r="A11" s="10"/>
       <c r="B11" s="17"/>
       <c r="C11" s="15" t="s">
@@ -835,7 +1257,7 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
     </row>
-    <row r="12" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="21.75" customHeight="true">
       <c r="A12" s="10"/>
       <c r="B12" s="17"/>
       <c r="C12" s="11" t="s">
@@ -853,7 +1275,7 @@
       <c r="M12" s="14"/>
       <c r="N12" s="14"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="21.75" customHeight="true">
       <c r="A13" s="10"/>
       <c r="B13" s="17"/>
       <c r="C13" s="8" t="s">
@@ -871,7 +1293,7 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
     </row>
-    <row r="14" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="12.75" customHeight="true">
       <c r="A14" s="10"/>
       <c r="B14" s="17"/>
       <c r="C14" s="10"/>
@@ -895,7 +1317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="12.75" customHeight="true">
       <c r="A15" s="10"/>
       <c r="B15" s="17"/>
       <c r="C15" s="10"/>
@@ -913,7 +1335,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="12.75" customHeight="true">
       <c r="A16" s="10"/>
       <c r="B16" s="17"/>
       <c r="C16" s="20"/>
@@ -931,7 +1353,7 @@
       <c r="M16" s="14"/>
       <c r="N16" s="14"/>
     </row>
-    <row r="17" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="21.75" customHeight="true">
       <c r="A17" s="10"/>
       <c r="B17" s="17"/>
       <c r="C17" s="21" t="s">
@@ -955,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="21.75" customHeight="true">
       <c r="A18" s="10"/>
       <c r="B18" s="17"/>
       <c r="C18" s="16" t="s">
@@ -973,7 +1395,7 @@
       <c r="M18" s="14"/>
       <c r="N18" s="14"/>
     </row>
-    <row r="19" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="12.75" customHeight="true">
       <c r="A19" s="10"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -991,7 +1413,7 @@
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
     </row>
-    <row r="20" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" ht="12.75" customHeight="true">
       <c r="A20" s="10"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -1015,7 +1437,7 @@
         <v>2210329</v>
       </c>
     </row>
-    <row r="21" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="12.75" customHeight="true">
       <c r="A21" s="10"/>
       <c r="B21" s="17"/>
       <c r="C21" s="22"/>
@@ -1039,7 +1461,7 @@
         <v>2210329</v>
       </c>
     </row>
-    <row r="22" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="21.75" customHeight="true">
       <c r="A22" s="10"/>
       <c r="B22" s="17"/>
       <c r="C22" s="11" t="s">
@@ -1057,7 +1479,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
     </row>
-    <row r="23" ht="21.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="21.75" customHeight="true">
       <c r="A23" s="10"/>
       <c r="B23" s="17"/>
       <c r="C23" s="21" t="s">
@@ -1083,7 +1505,7 @@
         <v>10599911</v>
       </c>
     </row>
-    <row r="24" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="12.75" customHeight="true">
       <c r="A24" s="20"/>
       <c r="B24" s="22"/>
       <c r="C24" s="11" t="s">
@@ -1111,7 +1533,7 @@
         <v>92617203</v>
       </c>
     </row>
-    <row r="25" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="12.75" customHeight="true">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1127,7 +1549,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="12.75" customHeight="true">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1143,7 +1565,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="12.75" customHeight="true">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1159,7 +1581,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="12.75" customHeight="true">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1175,7 +1597,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" ht="12.75" customHeight="true">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1191,7 +1613,7 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="12.75" customHeight="true">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1207,7 +1629,7 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="12.75" customHeight="true">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1223,7 +1645,7 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" ht="12.75" customHeight="true">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1239,7 +1661,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" ht="12.75" customHeight="true">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1255,7 +1677,7 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="12.75" customHeight="true">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1271,7 +1693,7 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" ht="12.75" customHeight="true">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1287,7 +1709,7 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="12.75" customHeight="true">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1303,7 +1725,7 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" ht="12.75" customHeight="true">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1319,7 +1741,7 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="12.75" customHeight="true">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1335,7 +1757,7 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" ht="12.75" customHeight="true">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1351,7 +1773,7 @@
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="12.75" customHeight="true">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1367,7 +1789,7 @@
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" ht="12.75" customHeight="true">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1383,7 +1805,7 @@
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" ht="12.75" customHeight="true">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1399,7 +1821,7 @@
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" ht="12.75" customHeight="true">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1415,7 +1837,7 @@
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" ht="12.75" customHeight="true">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1431,7 +1853,7 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" ht="12.75" customHeight="true">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1447,7 +1869,7 @@
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" ht="12.75" customHeight="true">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1463,7 +1885,7 @@
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" ht="12.75" customHeight="true">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1479,7 +1901,7 @@
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" ht="12.75" customHeight="true">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1495,7 +1917,7 @@
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
     </row>
-    <row r="49" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" ht="12.75" customHeight="true">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1511,7 +1933,7 @@
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
     </row>
-    <row r="50" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" ht="12.75" customHeight="true">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1527,7 +1949,7 @@
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" ht="12.75" customHeight="true">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1543,7 +1965,7 @@
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" ht="12.75" customHeight="true">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1559,7 +1981,7 @@
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
     </row>
-    <row r="53" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" ht="12.75" customHeight="true">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1575,7 +1997,7 @@
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" ht="12.75" customHeight="true">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1591,7 +2013,7 @@
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
     </row>
-    <row r="55" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" ht="12.75" customHeight="true">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1607,7 +2029,7 @@
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
     </row>
-    <row r="56" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" ht="12.75" customHeight="true">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1623,7 +2045,7 @@
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" ht="12.75" customHeight="true">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1639,7 +2061,7 @@
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" ht="12.75" customHeight="true">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1655,7 +2077,7 @@
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
     </row>
-    <row r="59" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" ht="12.75" customHeight="true">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1671,7 +2093,7 @@
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" ht="12.75" customHeight="true">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -1687,7 +2109,7 @@
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
     </row>
-    <row r="61" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" ht="12.75" customHeight="true">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1703,7 +2125,7 @@
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
     </row>
-    <row r="62" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" ht="12.75" customHeight="true">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1719,7 +2141,7 @@
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" ht="12.75" customHeight="true">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1735,7 +2157,7 @@
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
     </row>
-    <row r="64" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" ht="12.75" customHeight="true">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1751,7 +2173,7 @@
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
     </row>
-    <row r="65" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" ht="12.75" customHeight="true">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1767,7 +2189,7 @@
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
     </row>
-    <row r="66" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" ht="12.75" customHeight="true">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1783,7 +2205,7 @@
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
     </row>
-    <row r="67" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" ht="12.75" customHeight="true">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1799,7 +2221,7 @@
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
     </row>
-    <row r="68" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" ht="12.75" customHeight="true">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1815,7 +2237,7 @@
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
     </row>
-    <row r="69" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" ht="12.75" customHeight="true">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -1831,7 +2253,7 @@
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
     </row>
-    <row r="70" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" ht="12.75" customHeight="true">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -1847,7 +2269,7 @@
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
     </row>
-    <row r="71" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" ht="12.75" customHeight="true">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -1863,7 +2285,7 @@
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
     </row>
-    <row r="72" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" ht="12.75" customHeight="true">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -1879,7 +2301,7 @@
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
     </row>
-    <row r="73" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" ht="12.75" customHeight="true">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -1895,7 +2317,7 @@
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
     </row>
-    <row r="74" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" ht="12.75" customHeight="true">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -1911,7 +2333,7 @@
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
     </row>
-    <row r="75" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" ht="12.75" customHeight="true">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -1927,7 +2349,7 @@
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
     </row>
-    <row r="76" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" ht="12.75" customHeight="true">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -1943,7 +2365,7 @@
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
     </row>
-    <row r="77" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" ht="12.75" customHeight="true">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -1959,7 +2381,7 @@
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
     </row>
-    <row r="78" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" ht="12.75" customHeight="true">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -1975,7 +2397,7 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
     </row>
-    <row r="79" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" ht="12.75" customHeight="true">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -1991,7 +2413,7 @@
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
     </row>
-    <row r="80" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" ht="12.75" customHeight="true">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2007,7 +2429,7 @@
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
     </row>
-    <row r="81" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" ht="12.75" customHeight="true">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2023,7 +2445,7 @@
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
     </row>
-    <row r="82" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" ht="12.75" customHeight="true">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2039,7 +2461,7 @@
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
     </row>
-    <row r="83" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" ht="12.75" customHeight="true">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2055,7 +2477,7 @@
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
     </row>
-    <row r="84" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" ht="12.75" customHeight="true">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2071,7 +2493,7 @@
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
     </row>
-    <row r="85" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" ht="12.75" customHeight="true">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2087,7 +2509,7 @@
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
     </row>
-    <row r="86" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" ht="12.75" customHeight="true">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2103,7 +2525,7 @@
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
     </row>
-    <row r="87" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" ht="12.75" customHeight="true">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2119,7 +2541,7 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
     </row>
-    <row r="88" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" ht="12.75" customHeight="true">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2135,7 +2557,7 @@
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
     </row>
-    <row r="89" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" ht="12.75" customHeight="true">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2151,7 +2573,7 @@
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
     </row>
-    <row r="90" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" ht="12.75" customHeight="true">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2167,7 +2589,7 @@
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
     </row>
-    <row r="91" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" ht="12.75" customHeight="true">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2183,7 +2605,7 @@
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
     </row>
-    <row r="92" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" ht="12.75" customHeight="true">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2199,7 +2621,7 @@
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
     </row>
-    <row r="93" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" ht="12.75" customHeight="true">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2215,7 +2637,7 @@
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" ht="12.75" customHeight="true">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -2231,7 +2653,7 @@
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" ht="12.75" customHeight="true">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -2247,7 +2669,7 @@
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" ht="12.75" customHeight="true">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -2263,7 +2685,7 @@
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
     </row>
-    <row r="97" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" ht="12.75" customHeight="true">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -2279,7 +2701,7 @@
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
     </row>
-    <row r="98" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" ht="12.75" customHeight="true">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -2295,7 +2717,7 @@
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
     </row>
-    <row r="99" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" ht="12.75" customHeight="true">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -2311,7 +2733,7 @@
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
     </row>
-    <row r="100" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" ht="12.75" customHeight="true">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -2327,7 +2749,7 @@
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
     </row>
-    <row r="101" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" ht="12.75" customHeight="true">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -2343,7 +2765,7 @@
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
     </row>
-    <row r="102" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" ht="12.75" customHeight="true">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -2359,7 +2781,7 @@
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
     </row>
-    <row r="103" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" ht="12.75" customHeight="true">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -2375,7 +2797,7 @@
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
     </row>
-    <row r="104" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" ht="12.75" customHeight="true">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -2391,7 +2813,7 @@
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
     </row>
-    <row r="105" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" ht="12.75" customHeight="true">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -2407,7 +2829,7 @@
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
     </row>
-    <row r="106" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" ht="12.75" customHeight="true">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -2423,7 +2845,7 @@
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
     </row>
-    <row r="107" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" ht="12.75" customHeight="true">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -2439,7 +2861,7 @@
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
     </row>
-    <row r="108" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" ht="12.75" customHeight="true">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -2455,7 +2877,7 @@
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
     </row>
-    <row r="109" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" ht="12.75" customHeight="true">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -2471,7 +2893,7 @@
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
     </row>
-    <row r="110" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" ht="12.75" customHeight="true">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -2487,7 +2909,7 @@
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
     </row>
-    <row r="111" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" ht="12.75" customHeight="true">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -2503,7 +2925,7 @@
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
     </row>
-    <row r="112" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" ht="12.75" customHeight="true">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -2519,7 +2941,7 @@
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
     </row>
-    <row r="113" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" ht="12.75" customHeight="true">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -2535,7 +2957,7 @@
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
     </row>
-    <row r="114" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" ht="12.75" customHeight="true">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -2551,7 +2973,7 @@
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
     </row>
-    <row r="115" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" ht="12.75" customHeight="true">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -2567,7 +2989,7 @@
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
     </row>
-    <row r="116" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" ht="12.75" customHeight="true">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -2583,7 +3005,7 @@
       <c r="M116" s="1"/>
       <c r="N116" s="1"/>
     </row>
-    <row r="117" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" ht="12.75" customHeight="true">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -2599,7 +3021,7 @@
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
     </row>
-    <row r="118" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" ht="12.75" customHeight="true">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -2615,7 +3037,7 @@
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
     </row>
-    <row r="119" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" ht="12.75" customHeight="true">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -2631,7 +3053,7 @@
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
     </row>
-    <row r="120" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" ht="12.75" customHeight="true">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -2647,7 +3069,7 @@
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
     </row>
-    <row r="121" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" ht="12.75" customHeight="true">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -2663,7 +3085,7 @@
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
     </row>
-    <row r="122" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" ht="12.75" customHeight="true">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -2679,7 +3101,7 @@
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
     </row>
-    <row r="123" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" ht="12.75" customHeight="true">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -2695,7 +3117,7 @@
       <c r="M123" s="1"/>
       <c r="N123" s="1"/>
     </row>
-    <row r="124" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" ht="12.75" customHeight="true">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -2711,7 +3133,7 @@
       <c r="M124" s="1"/>
       <c r="N124" s="1"/>
     </row>
-    <row r="125" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" ht="12.75" customHeight="true">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -2727,7 +3149,7 @@
       <c r="M125" s="1"/>
       <c r="N125" s="1"/>
     </row>
-    <row r="126" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" ht="12.75" customHeight="true">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -2743,7 +3165,7 @@
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
     </row>
-    <row r="127" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" ht="12.75" customHeight="true">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -2759,7 +3181,7 @@
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
     </row>
-    <row r="128" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" ht="12.75" customHeight="true">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -2775,7 +3197,7 @@
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
     </row>
-    <row r="129" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" ht="12.75" customHeight="true">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -2791,7 +3213,7 @@
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
     </row>
-    <row r="130" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" ht="12.75" customHeight="true">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -2807,7 +3229,7 @@
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
     </row>
-    <row r="131" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" ht="12.75" customHeight="true">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -2823,7 +3245,7 @@
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
     </row>
-    <row r="132" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" ht="12.75" customHeight="true">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -2839,7 +3261,7 @@
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
     </row>
-    <row r="133" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" ht="12.75" customHeight="true">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -2855,7 +3277,7 @@
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
     </row>
-    <row r="134" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" ht="12.75" customHeight="true">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -2871,7 +3293,7 @@
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
     </row>
-    <row r="135" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" ht="12.75" customHeight="true">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -2887,7 +3309,7 @@
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
     </row>
-    <row r="136" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" ht="12.75" customHeight="true">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -2903,7 +3325,7 @@
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
     </row>
-    <row r="137" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" ht="12.75" customHeight="true">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -2919,7 +3341,7 @@
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
     </row>
-    <row r="138" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" ht="12.75" customHeight="true">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -2935,7 +3357,7 @@
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
     </row>
-    <row r="139" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" ht="12.75" customHeight="true">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -2951,7 +3373,7 @@
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
     </row>
-    <row r="140" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" ht="12.75" customHeight="true">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -2967,7 +3389,7 @@
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
     </row>
-    <row r="141" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" ht="12.75" customHeight="true">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -2983,7 +3405,7 @@
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
     </row>
-    <row r="142" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" ht="12.75" customHeight="true">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -2999,7 +3421,7 @@
       <c r="M142" s="1"/>
       <c r="N142" s="1"/>
     </row>
-    <row r="143" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" ht="12.75" customHeight="true">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -3015,7 +3437,7 @@
       <c r="M143" s="1"/>
       <c r="N143" s="1"/>
     </row>
-    <row r="144" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" ht="12.75" customHeight="true">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -3031,7 +3453,7 @@
       <c r="M144" s="1"/>
       <c r="N144" s="1"/>
     </row>
-    <row r="145" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" ht="12.75" customHeight="true">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -3047,7 +3469,7 @@
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
     </row>
-    <row r="146" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" ht="12.75" customHeight="true">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -3063,7 +3485,7 @@
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
     </row>
-    <row r="147" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" ht="12.75" customHeight="true">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -3079,7 +3501,7 @@
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
     </row>
-    <row r="148" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" ht="12.75" customHeight="true">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -3095,7 +3517,7 @@
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
     </row>
-    <row r="149" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" ht="12.75" customHeight="true">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -3111,7 +3533,7 @@
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
     </row>
-    <row r="150" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" ht="12.75" customHeight="true">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -3127,7 +3549,7 @@
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
     </row>
-    <row r="151" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" ht="12.75" customHeight="true">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -3143,7 +3565,7 @@
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
     </row>
-    <row r="152" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" ht="12.75" customHeight="true">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -3159,7 +3581,7 @@
       <c r="M152" s="1"/>
       <c r="N152" s="1"/>
     </row>
-    <row r="153" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" ht="12.75" customHeight="true">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -3175,7 +3597,7 @@
       <c r="M153" s="1"/>
       <c r="N153" s="1"/>
     </row>
-    <row r="154" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" ht="12.75" customHeight="true">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -3191,7 +3613,7 @@
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
     </row>
-    <row r="155" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" ht="12.75" customHeight="true">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -3207,7 +3629,7 @@
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
     </row>
-    <row r="156" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" ht="12.75" customHeight="true">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -3223,7 +3645,7 @@
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
     </row>
-    <row r="157" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" ht="12.75" customHeight="true">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -3239,7 +3661,7 @@
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
     </row>
-    <row r="158" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" ht="12.75" customHeight="true">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -3255,7 +3677,7 @@
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
     </row>
-    <row r="159" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" ht="12.75" customHeight="true">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -3271,7 +3693,7 @@
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
     </row>
-    <row r="160" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" ht="12.75" customHeight="true">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -3287,7 +3709,7 @@
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
     </row>
-    <row r="161" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" ht="12.75" customHeight="true">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -3303,7 +3725,7 @@
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
     </row>
-    <row r="162" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" ht="12.75" customHeight="true">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -3319,7 +3741,7 @@
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
     </row>
-    <row r="163" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" ht="12.75" customHeight="true">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -3335,7 +3757,7 @@
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
     </row>
-    <row r="164" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" ht="12.75" customHeight="true">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -3351,7 +3773,7 @@
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
     </row>
-    <row r="165" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" ht="12.75" customHeight="true">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -3367,7 +3789,7 @@
       <c r="M165" s="1"/>
       <c r="N165" s="1"/>
     </row>
-    <row r="166" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" ht="12.75" customHeight="true">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -3383,7 +3805,7 @@
       <c r="M166" s="1"/>
       <c r="N166" s="1"/>
     </row>
-    <row r="167" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" ht="12.75" customHeight="true">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -3399,7 +3821,7 @@
       <c r="M167" s="1"/>
       <c r="N167" s="1"/>
     </row>
-    <row r="168" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" ht="12.75" customHeight="true">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -3415,7 +3837,7 @@
       <c r="M168" s="1"/>
       <c r="N168" s="1"/>
     </row>
-    <row r="169" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" ht="12.75" customHeight="true">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -3431,7 +3853,7 @@
       <c r="M169" s="1"/>
       <c r="N169" s="1"/>
     </row>
-    <row r="170" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" ht="12.75" customHeight="true">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -3447,7 +3869,7 @@
       <c r="M170" s="1"/>
       <c r="N170" s="1"/>
     </row>
-    <row r="171" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" ht="12.75" customHeight="true">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -3463,7 +3885,7 @@
       <c r="M171" s="1"/>
       <c r="N171" s="1"/>
     </row>
-    <row r="172" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" ht="12.75" customHeight="true">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -3479,7 +3901,7 @@
       <c r="M172" s="1"/>
       <c r="N172" s="1"/>
     </row>
-    <row r="173" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" ht="12.75" customHeight="true">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -3495,7 +3917,7 @@
       <c r="M173" s="1"/>
       <c r="N173" s="1"/>
     </row>
-    <row r="174" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" ht="12.75" customHeight="true">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -3511,7 +3933,7 @@
       <c r="M174" s="1"/>
       <c r="N174" s="1"/>
     </row>
-    <row r="175" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" ht="12.75" customHeight="true">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -3527,7 +3949,7 @@
       <c r="M175" s="1"/>
       <c r="N175" s="1"/>
     </row>
-    <row r="176" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" ht="12.75" customHeight="true">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -3543,7 +3965,7 @@
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
     </row>
-    <row r="177" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" ht="12.75" customHeight="true">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -3559,7 +3981,7 @@
       <c r="M177" s="1"/>
       <c r="N177" s="1"/>
     </row>
-    <row r="178" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" ht="12.75" customHeight="true">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -3575,7 +3997,7 @@
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
     </row>
-    <row r="179" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" ht="12.75" customHeight="true">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -3591,7 +4013,7 @@
       <c r="M179" s="1"/>
       <c r="N179" s="1"/>
     </row>
-    <row r="180" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" ht="12.75" customHeight="true">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -3607,7 +4029,7 @@
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
     </row>
-    <row r="181" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" ht="12.75" customHeight="true">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -3623,7 +4045,7 @@
       <c r="M181" s="1"/>
       <c r="N181" s="1"/>
     </row>
-    <row r="182" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" ht="12.75" customHeight="true">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -3639,7 +4061,7 @@
       <c r="M182" s="1"/>
       <c r="N182" s="1"/>
     </row>
-    <row r="183" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" ht="12.75" customHeight="true">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -3655,7 +4077,7 @@
       <c r="M183" s="1"/>
       <c r="N183" s="1"/>
     </row>
-    <row r="184" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" ht="12.75" customHeight="true">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -3671,7 +4093,7 @@
       <c r="M184" s="1"/>
       <c r="N184" s="1"/>
     </row>
-    <row r="185" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" ht="12.75" customHeight="true">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -3687,7 +4109,7 @@
       <c r="M185" s="1"/>
       <c r="N185" s="1"/>
     </row>
-    <row r="186" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" ht="12.75" customHeight="true">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -3703,7 +4125,7 @@
       <c r="M186" s="1"/>
       <c r="N186" s="1"/>
     </row>
-    <row r="187" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" ht="12.75" customHeight="true">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -3719,7 +4141,7 @@
       <c r="M187" s="1"/>
       <c r="N187" s="1"/>
     </row>
-    <row r="188" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" ht="12.75" customHeight="true">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -3735,7 +4157,7 @@
       <c r="M188" s="1"/>
       <c r="N188" s="1"/>
     </row>
-    <row r="189" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" ht="12.75" customHeight="true">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -3751,7 +4173,7 @@
       <c r="M189" s="1"/>
       <c r="N189" s="1"/>
     </row>
-    <row r="190" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" ht="12.75" customHeight="true">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -3767,7 +4189,7 @@
       <c r="M190" s="1"/>
       <c r="N190" s="1"/>
     </row>
-    <row r="191" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" ht="12.75" customHeight="true">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -3783,7 +4205,7 @@
       <c r="M191" s="1"/>
       <c r="N191" s="1"/>
     </row>
-    <row r="192" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" ht="12.75" customHeight="true">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -3799,7 +4221,7 @@
       <c r="M192" s="1"/>
       <c r="N192" s="1"/>
     </row>
-    <row r="193" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" ht="12.75" customHeight="true">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -3815,7 +4237,7 @@
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
     </row>
-    <row r="194" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" ht="12.75" customHeight="true">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -3831,7 +4253,7 @@
       <c r="M194" s="1"/>
       <c r="N194" s="1"/>
     </row>
-    <row r="195" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" ht="12.75" customHeight="true">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -3847,7 +4269,7 @@
       <c r="M195" s="1"/>
       <c r="N195" s="1"/>
     </row>
-    <row r="196" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" ht="12.75" customHeight="true">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -3863,7 +4285,7 @@
       <c r="M196" s="1"/>
       <c r="N196" s="1"/>
     </row>
-    <row r="197" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" ht="12.75" customHeight="true">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -3879,7 +4301,7 @@
       <c r="M197" s="1"/>
       <c r="N197" s="1"/>
     </row>
-    <row r="198" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" ht="12.75" customHeight="true">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -3895,7 +4317,7 @@
       <c r="M198" s="1"/>
       <c r="N198" s="1"/>
     </row>
-    <row r="199" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" ht="12.75" customHeight="true">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -3911,7 +4333,7 @@
       <c r="M199" s="1"/>
       <c r="N199" s="1"/>
     </row>
-    <row r="200" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" ht="12.75" customHeight="true">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -3927,7 +4349,7 @@
       <c r="M200" s="1"/>
       <c r="N200" s="1"/>
     </row>
-    <row r="201" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" ht="12.75" customHeight="true">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -3943,7 +4365,7 @@
       <c r="M201" s="1"/>
       <c r="N201" s="1"/>
     </row>
-    <row r="202" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" ht="12.75" customHeight="true">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -3959,7 +4381,7 @@
       <c r="M202" s="1"/>
       <c r="N202" s="1"/>
     </row>
-    <row r="203" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" ht="12.75" customHeight="true">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -3975,7 +4397,7 @@
       <c r="M203" s="1"/>
       <c r="N203" s="1"/>
     </row>
-    <row r="204" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" ht="12.75" customHeight="true">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -3991,7 +4413,7 @@
       <c r="M204" s="1"/>
       <c r="N204" s="1"/>
     </row>
-    <row r="205" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" ht="12.75" customHeight="true">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -4007,7 +4429,7 @@
       <c r="M205" s="1"/>
       <c r="N205" s="1"/>
     </row>
-    <row r="206" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" ht="12.75" customHeight="true">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -4023,7 +4445,7 @@
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
     </row>
-    <row r="207" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" ht="12.75" customHeight="true">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -4039,7 +4461,7 @@
       <c r="M207" s="1"/>
       <c r="N207" s="1"/>
     </row>
-    <row r="208" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" ht="12.75" customHeight="true">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -4055,7 +4477,7 @@
       <c r="M208" s="1"/>
       <c r="N208" s="1"/>
     </row>
-    <row r="209" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" ht="12.75" customHeight="true">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -4071,7 +4493,7 @@
       <c r="M209" s="1"/>
       <c r="N209" s="1"/>
     </row>
-    <row r="210" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" ht="12.75" customHeight="true">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -4087,7 +4509,7 @@
       <c r="M210" s="1"/>
       <c r="N210" s="1"/>
     </row>
-    <row r="211" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" ht="12.75" customHeight="true">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -4103,7 +4525,7 @@
       <c r="M211" s="1"/>
       <c r="N211" s="1"/>
     </row>
-    <row r="212" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" ht="12.75" customHeight="true">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -4119,7 +4541,7 @@
       <c r="M212" s="1"/>
       <c r="N212" s="1"/>
     </row>
-    <row r="213" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" ht="12.75" customHeight="true">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -4135,7 +4557,7 @@
       <c r="M213" s="1"/>
       <c r="N213" s="1"/>
     </row>
-    <row r="214" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" ht="12.75" customHeight="true">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -4151,7 +4573,7 @@
       <c r="M214" s="1"/>
       <c r="N214" s="1"/>
     </row>
-    <row r="215" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" ht="12.75" customHeight="true">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -4167,7 +4589,7 @@
       <c r="M215" s="1"/>
       <c r="N215" s="1"/>
     </row>
-    <row r="216" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" ht="12.75" customHeight="true">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -4183,7 +4605,7 @@
       <c r="M216" s="1"/>
       <c r="N216" s="1"/>
     </row>
-    <row r="217" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" ht="12.75" customHeight="true">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -4199,7 +4621,7 @@
       <c r="M217" s="1"/>
       <c r="N217" s="1"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" ht="12.75" customHeight="true">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -4215,7 +4637,7 @@
       <c r="M218" s="1"/>
       <c r="N218" s="1"/>
     </row>
-    <row r="219" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" ht="12.75" customHeight="true">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -4231,7 +4653,7 @@
       <c r="M219" s="1"/>
       <c r="N219" s="1"/>
     </row>
-    <row r="220" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" ht="12.75" customHeight="true">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -4247,7 +4669,7 @@
       <c r="M220" s="1"/>
       <c r="N220" s="1"/>
     </row>
-    <row r="221" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" ht="12.75" customHeight="true">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -4263,7 +4685,7 @@
       <c r="M221" s="1"/>
       <c r="N221" s="1"/>
     </row>
-    <row r="222" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" ht="12.75" customHeight="true">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -4279,7 +4701,7 @@
       <c r="M222" s="1"/>
       <c r="N222" s="1"/>
     </row>
-    <row r="223" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" ht="12.75" customHeight="true">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -4295,7 +4717,7 @@
       <c r="M223" s="1"/>
       <c r="N223" s="1"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" ht="12.75" customHeight="true">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -4311,7 +4733,7 @@
       <c r="M224" s="1"/>
       <c r="N224" s="1"/>
     </row>
-    <row r="225" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" ht="12.75" customHeight="true">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -4327,7 +4749,7 @@
       <c r="M225" s="1"/>
       <c r="N225" s="1"/>
     </row>
-    <row r="226" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" ht="12.75" customHeight="true">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -4343,7 +4765,7 @@
       <c r="M226" s="1"/>
       <c r="N226" s="1"/>
     </row>
-    <row r="227" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" ht="12.75" customHeight="true">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -4359,7 +4781,7 @@
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
     </row>
-    <row r="228" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" ht="12.75" customHeight="true">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -4375,7 +4797,7 @@
       <c r="M228" s="1"/>
       <c r="N228" s="1"/>
     </row>
-    <row r="229" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" ht="12.75" customHeight="true">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -4391,7 +4813,7 @@
       <c r="M229" s="1"/>
       <c r="N229" s="1"/>
     </row>
-    <row r="230" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" ht="12.75" customHeight="true">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -4407,7 +4829,7 @@
       <c r="M230" s="1"/>
       <c r="N230" s="1"/>
     </row>
-    <row r="231" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" ht="12.75" customHeight="true">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -4423,7 +4845,7 @@
       <c r="M231" s="1"/>
       <c r="N231" s="1"/>
     </row>
-    <row r="232" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" ht="12.75" customHeight="true">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -4439,7 +4861,7 @@
       <c r="M232" s="1"/>
       <c r="N232" s="1"/>
     </row>
-    <row r="233" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" ht="12.75" customHeight="true">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -4455,7 +4877,7 @@
       <c r="M233" s="1"/>
       <c r="N233" s="1"/>
     </row>
-    <row r="234" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" ht="12.75" customHeight="true">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -4471,7 +4893,7 @@
       <c r="M234" s="1"/>
       <c r="N234" s="1"/>
     </row>
-    <row r="235" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" ht="12.75" customHeight="true">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -4487,7 +4909,7 @@
       <c r="M235" s="1"/>
       <c r="N235" s="1"/>
     </row>
-    <row r="236" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" ht="12.75" customHeight="true">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -4503,7 +4925,7 @@
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
     </row>
-    <row r="237" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" ht="12.75" customHeight="true">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -4519,7 +4941,7 @@
       <c r="M237" s="1"/>
       <c r="N237" s="1"/>
     </row>
-    <row r="238" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" ht="12.75" customHeight="true">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -4535,7 +4957,7 @@
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
     </row>
-    <row r="239" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" ht="12.75" customHeight="true">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -4551,7 +4973,7 @@
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
     </row>
-    <row r="240" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" ht="12.75" customHeight="true">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -4567,7 +4989,7 @@
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
     </row>
-    <row r="241" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" ht="12.75" customHeight="true">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -4583,7 +5005,7 @@
       <c r="M241" s="1"/>
       <c r="N241" s="1"/>
     </row>
-    <row r="242" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" ht="12.75" customHeight="true">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -4599,7 +5021,7 @@
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
     </row>
-    <row r="243" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" ht="12.75" customHeight="true">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -4615,7 +5037,7 @@
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
     </row>
-    <row r="244" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" ht="12.75" customHeight="true">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -4631,7 +5053,7 @@
       <c r="M244" s="1"/>
       <c r="N244" s="1"/>
     </row>
-    <row r="245" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" ht="12.75" customHeight="true">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -4647,7 +5069,7 @@
       <c r="M245" s="1"/>
       <c r="N245" s="1"/>
     </row>
-    <row r="246" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" ht="12.75" customHeight="true">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -4663,7 +5085,7 @@
       <c r="M246" s="1"/>
       <c r="N246" s="1"/>
     </row>
-    <row r="247" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" ht="12.75" customHeight="true">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -4679,7 +5101,7 @@
       <c r="M247" s="1"/>
       <c r="N247" s="1"/>
     </row>
-    <row r="248" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" ht="12.75" customHeight="true">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -4695,7 +5117,7 @@
       <c r="M248" s="1"/>
       <c r="N248" s="1"/>
     </row>
-    <row r="249" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" ht="12.75" customHeight="true">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -4711,7 +5133,7 @@
       <c r="M249" s="1"/>
       <c r="N249" s="1"/>
     </row>
-    <row r="250" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" ht="12.75" customHeight="true">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -4727,7 +5149,7 @@
       <c r="M250" s="1"/>
       <c r="N250" s="1"/>
     </row>
-    <row r="251" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" ht="12.75" customHeight="true">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -4743,7 +5165,7 @@
       <c r="M251" s="1"/>
       <c r="N251" s="1"/>
     </row>
-    <row r="252" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" ht="12.75" customHeight="true">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -4759,7 +5181,7 @@
       <c r="M252" s="1"/>
       <c r="N252" s="1"/>
     </row>
-    <row r="253" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" ht="12.75" customHeight="true">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -4775,7 +5197,7 @@
       <c r="M253" s="1"/>
       <c r="N253" s="1"/>
     </row>
-    <row r="254" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" ht="12.75" customHeight="true">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -4791,7 +5213,7 @@
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
     </row>
-    <row r="255" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" ht="12.75" customHeight="true">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -4807,7 +5229,7 @@
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
     </row>
-    <row r="256" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" ht="12.75" customHeight="true">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -4823,7 +5245,7 @@
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
     </row>
-    <row r="257" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" ht="12.75" customHeight="true">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -4839,7 +5261,7 @@
       <c r="M257" s="1"/>
       <c r="N257" s="1"/>
     </row>
-    <row r="258" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" ht="12.75" customHeight="true">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -4855,7 +5277,7 @@
       <c r="M258" s="1"/>
       <c r="N258" s="1"/>
     </row>
-    <row r="259" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" ht="12.75" customHeight="true">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -4871,7 +5293,7 @@
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
     </row>
-    <row r="260" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" ht="12.75" customHeight="true">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -4887,7 +5309,7 @@
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
     </row>
-    <row r="261" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" ht="12.75" customHeight="true">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -4903,7 +5325,7 @@
       <c r="M261" s="1"/>
       <c r="N261" s="1"/>
     </row>
-    <row r="262" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" ht="12.75" customHeight="true">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -4919,7 +5341,7 @@
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
     </row>
-    <row r="263" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" ht="12.75" customHeight="true">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -4935,7 +5357,7 @@
       <c r="M263" s="1"/>
       <c r="N263" s="1"/>
     </row>
-    <row r="264" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" ht="12.75" customHeight="true">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -4951,7 +5373,7 @@
       <c r="M264" s="1"/>
       <c r="N264" s="1"/>
     </row>
-    <row r="265" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" ht="12.75" customHeight="true">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -4967,7 +5389,7 @@
       <c r="M265" s="1"/>
       <c r="N265" s="1"/>
     </row>
-    <row r="266" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" ht="12.75" customHeight="true">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -4983,7 +5405,7 @@
       <c r="M266" s="1"/>
       <c r="N266" s="1"/>
     </row>
-    <row r="267" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" ht="12.75" customHeight="true">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -4999,7 +5421,7 @@
       <c r="M267" s="1"/>
       <c r="N267" s="1"/>
     </row>
-    <row r="268" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" ht="12.75" customHeight="true">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -5015,7 +5437,7 @@
       <c r="M268" s="1"/>
       <c r="N268" s="1"/>
     </row>
-    <row r="269" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" ht="12.75" customHeight="true">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -5031,7 +5453,7 @@
       <c r="M269" s="1"/>
       <c r="N269" s="1"/>
     </row>
-    <row r="270" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" ht="12.75" customHeight="true">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -5047,7 +5469,7 @@
       <c r="M270" s="1"/>
       <c r="N270" s="1"/>
     </row>
-    <row r="271" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" ht="12.75" customHeight="true">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -5063,7 +5485,7 @@
       <c r="M271" s="1"/>
       <c r="N271" s="1"/>
     </row>
-    <row r="272" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" ht="12.75" customHeight="true">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -5079,7 +5501,7 @@
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
     </row>
-    <row r="273" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" ht="12.75" customHeight="true">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -5095,7 +5517,7 @@
       <c r="M273" s="1"/>
       <c r="N273" s="1"/>
     </row>
-    <row r="274" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" ht="12.75" customHeight="true">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -5111,7 +5533,7 @@
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
     </row>
-    <row r="275" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" ht="12.75" customHeight="true">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -5127,7 +5549,7 @@
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
     </row>
-    <row r="276" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" ht="12.75" customHeight="true">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -5143,7 +5565,7 @@
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
     </row>
-    <row r="277" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" ht="12.75" customHeight="true">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -5159,7 +5581,7 @@
       <c r="M277" s="1"/>
       <c r="N277" s="1"/>
     </row>
-    <row r="278" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" ht="12.75" customHeight="true">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -5175,7 +5597,7 @@
       <c r="M278" s="1"/>
       <c r="N278" s="1"/>
     </row>
-    <row r="279" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" ht="12.75" customHeight="true">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -5191,7 +5613,7 @@
       <c r="M279" s="1"/>
       <c r="N279" s="1"/>
     </row>
-    <row r="280" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" ht="12.75" customHeight="true">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -5207,7 +5629,7 @@
       <c r="M280" s="1"/>
       <c r="N280" s="1"/>
     </row>
-    <row r="281" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" ht="12.75" customHeight="true">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -5223,7 +5645,7 @@
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
     </row>
-    <row r="282" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" ht="12.75" customHeight="true">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -5239,7 +5661,7 @@
       <c r="M282" s="1"/>
       <c r="N282" s="1"/>
     </row>
-    <row r="283" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" ht="12.75" customHeight="true">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -5255,7 +5677,7 @@
       <c r="M283" s="1"/>
       <c r="N283" s="1"/>
     </row>
-    <row r="284" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" ht="12.75" customHeight="true">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -5271,7 +5693,7 @@
       <c r="M284" s="1"/>
       <c r="N284" s="1"/>
     </row>
-    <row r="285" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" ht="12.75" customHeight="true">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -5287,7 +5709,7 @@
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
     </row>
-    <row r="286" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" ht="12.75" customHeight="true">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -5303,7 +5725,7 @@
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
     </row>
-    <row r="287" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" ht="12.75" customHeight="true">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -5319,7 +5741,7 @@
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
     </row>
-    <row r="288" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" ht="12.75" customHeight="true">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -5335,7 +5757,7 @@
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
     </row>
-    <row r="289" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" ht="12.75" customHeight="true">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -5351,7 +5773,7 @@
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
     </row>
-    <row r="290" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" ht="12.75" customHeight="true">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -5367,7 +5789,7 @@
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
     </row>
-    <row r="291" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" ht="12.75" customHeight="true">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -5383,7 +5805,7 @@
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
     </row>
-    <row r="292" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" ht="12.75" customHeight="true">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -5399,7 +5821,7 @@
       <c r="M292" s="1"/>
       <c r="N292" s="1"/>
     </row>
-    <row r="293" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" ht="12.75" customHeight="true">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -5415,7 +5837,7 @@
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
     </row>
-    <row r="294" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" ht="12.75" customHeight="true">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -5431,7 +5853,7 @@
       <c r="M294" s="1"/>
       <c r="N294" s="1"/>
     </row>
-    <row r="295" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" ht="12.75" customHeight="true">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -5447,7 +5869,7 @@
       <c r="M295" s="1"/>
       <c r="N295" s="1"/>
     </row>
-    <row r="296" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" ht="12.75" customHeight="true">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -5463,7 +5885,7 @@
       <c r="M296" s="1"/>
       <c r="N296" s="1"/>
     </row>
-    <row r="297" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" ht="12.75" customHeight="true">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -5479,7 +5901,7 @@
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
     </row>
-    <row r="298" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" ht="12.75" customHeight="true">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -5495,7 +5917,7 @@
       <c r="M298" s="1"/>
       <c r="N298" s="1"/>
     </row>
-    <row r="299" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" ht="12.75" customHeight="true">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -5511,7 +5933,7 @@
       <c r="M299" s="1"/>
       <c r="N299" s="1"/>
     </row>
-    <row r="300" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" ht="12.75" customHeight="true">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -5527,7 +5949,7 @@
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
     </row>
-    <row r="301" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" ht="12.75" customHeight="true">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -5543,7 +5965,7 @@
       <c r="M301" s="1"/>
       <c r="N301" s="1"/>
     </row>
-    <row r="302" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" ht="12.75" customHeight="true">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -5559,7 +5981,7 @@
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
     </row>
-    <row r="303" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" ht="12.75" customHeight="true">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -5575,7 +5997,7 @@
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
     </row>
-    <row r="304" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" ht="12.75" customHeight="true">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -5591,7 +6013,7 @@
       <c r="M304" s="1"/>
       <c r="N304" s="1"/>
     </row>
-    <row r="305" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" ht="12.75" customHeight="true">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -5607,7 +6029,7 @@
       <c r="M305" s="1"/>
       <c r="N305" s="1"/>
     </row>
-    <row r="306" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" ht="12.75" customHeight="true">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -5623,7 +6045,7 @@
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
     </row>
-    <row r="307" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" ht="12.75" customHeight="true">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -5639,7 +6061,7 @@
       <c r="M307" s="1"/>
       <c r="N307" s="1"/>
     </row>
-    <row r="308" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" ht="12.75" customHeight="true">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -5655,7 +6077,7 @@
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
     </row>
-    <row r="309" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" ht="12.75" customHeight="true">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -5671,7 +6093,7 @@
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
     </row>
-    <row r="310" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" ht="12.75" customHeight="true">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -5687,7 +6109,7 @@
       <c r="M310" s="1"/>
       <c r="N310" s="1"/>
     </row>
-    <row r="311" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" ht="12.75" customHeight="true">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -5703,7 +6125,7 @@
       <c r="M311" s="1"/>
       <c r="N311" s="1"/>
     </row>
-    <row r="312" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" ht="12.75" customHeight="true">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -5719,7 +6141,7 @@
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
     </row>
-    <row r="313" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" ht="12.75" customHeight="true">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -5735,7 +6157,7 @@
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
     </row>
-    <row r="314" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" ht="12.75" customHeight="true">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -5751,7 +6173,7 @@
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
     </row>
-    <row r="315" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" ht="12.75" customHeight="true">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -5767,7 +6189,7 @@
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
     </row>
-    <row r="316" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" ht="12.75" customHeight="true">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -5783,7 +6205,7 @@
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
     </row>
-    <row r="317" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" ht="12.75" customHeight="true">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -5799,7 +6221,7 @@
       <c r="M317" s="1"/>
       <c r="N317" s="1"/>
     </row>
-    <row r="318" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" ht="12.75" customHeight="true">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -5815,7 +6237,7 @@
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
     </row>
-    <row r="319" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" ht="12.75" customHeight="true">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -5831,7 +6253,7 @@
       <c r="M319" s="1"/>
       <c r="N319" s="1"/>
     </row>
-    <row r="320" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" ht="12.75" customHeight="true">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -5847,7 +6269,7 @@
       <c r="M320" s="1"/>
       <c r="N320" s="1"/>
     </row>
-    <row r="321" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" ht="12.75" customHeight="true">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -5863,7 +6285,7 @@
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
     </row>
-    <row r="322" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" ht="12.75" customHeight="true">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -5879,7 +6301,7 @@
       <c r="M322" s="1"/>
       <c r="N322" s="1"/>
     </row>
-    <row r="323" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" ht="12.75" customHeight="true">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -5895,7 +6317,7 @@
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
     </row>
-    <row r="324" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" ht="12.75" customHeight="true">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -5911,7 +6333,7 @@
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
     </row>
-    <row r="325" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" ht="12.75" customHeight="true">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -5927,7 +6349,7 @@
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
     </row>
-    <row r="326" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" ht="12.75" customHeight="true">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -5943,7 +6365,7 @@
       <c r="M326" s="1"/>
       <c r="N326" s="1"/>
     </row>
-    <row r="327" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" ht="12.75" customHeight="true">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -5959,7 +6381,7 @@
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
     </row>
-    <row r="328" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" ht="12.75" customHeight="true">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -5975,7 +6397,7 @@
       <c r="M328" s="1"/>
       <c r="N328" s="1"/>
     </row>
-    <row r="329" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" ht="12.75" customHeight="true">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -5991,7 +6413,7 @@
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
     </row>
-    <row r="330" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" ht="12.75" customHeight="true">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -6007,7 +6429,7 @@
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
     </row>
-    <row r="331" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" ht="12.75" customHeight="true">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -6023,7 +6445,7 @@
       <c r="M331" s="1"/>
       <c r="N331" s="1"/>
     </row>
-    <row r="332" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" ht="12.75" customHeight="true">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -6039,7 +6461,7 @@
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
     </row>
-    <row r="333" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" ht="12.75" customHeight="true">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -6055,7 +6477,7 @@
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
     </row>
-    <row r="334" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" ht="12.75" customHeight="true">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -6071,7 +6493,7 @@
       <c r="M334" s="1"/>
       <c r="N334" s="1"/>
     </row>
-    <row r="335" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" ht="12.75" customHeight="true">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -6087,7 +6509,7 @@
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
     </row>
-    <row r="336" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" ht="12.75" customHeight="true">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -6103,7 +6525,7 @@
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
     </row>
-    <row r="337" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" ht="12.75" customHeight="true">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -6119,7 +6541,7 @@
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
     </row>
-    <row r="338" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" ht="12.75" customHeight="true">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -6135,7 +6557,7 @@
       <c r="M338" s="1"/>
       <c r="N338" s="1"/>
     </row>
-    <row r="339" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" ht="12.75" customHeight="true">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -6151,7 +6573,7 @@
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
     </row>
-    <row r="340" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" ht="12.75" customHeight="true">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -6167,7 +6589,7 @@
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
     </row>
-    <row r="341" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" ht="12.75" customHeight="true">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -6183,7 +6605,7 @@
       <c r="M341" s="1"/>
       <c r="N341" s="1"/>
     </row>
-    <row r="342" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" ht="12.75" customHeight="true">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -6199,7 +6621,7 @@
       <c r="M342" s="1"/>
       <c r="N342" s="1"/>
     </row>
-    <row r="343" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" ht="12.75" customHeight="true">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -6215,7 +6637,7 @@
       <c r="M343" s="1"/>
       <c r="N343" s="1"/>
     </row>
-    <row r="344" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" ht="12.75" customHeight="true">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -6231,7 +6653,7 @@
       <c r="M344" s="1"/>
       <c r="N344" s="1"/>
     </row>
-    <row r="345" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" ht="12.75" customHeight="true">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -6247,7 +6669,7 @@
       <c r="M345" s="1"/>
       <c r="N345" s="1"/>
     </row>
-    <row r="346" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" ht="12.75" customHeight="true">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -6263,7 +6685,7 @@
       <c r="M346" s="1"/>
       <c r="N346" s="1"/>
     </row>
-    <row r="347" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" ht="12.75" customHeight="true">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -6279,7 +6701,7 @@
       <c r="M347" s="1"/>
       <c r="N347" s="1"/>
     </row>
-    <row r="348" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" ht="12.75" customHeight="true">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -6295,7 +6717,7 @@
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
     </row>
-    <row r="349" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" ht="12.75" customHeight="true">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -6311,7 +6733,7 @@
       <c r="M349" s="1"/>
       <c r="N349" s="1"/>
     </row>
-    <row r="350" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" ht="12.75" customHeight="true">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -6327,7 +6749,7 @@
       <c r="M350" s="1"/>
       <c r="N350" s="1"/>
     </row>
-    <row r="351" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" ht="12.75" customHeight="true">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -6343,7 +6765,7 @@
       <c r="M351" s="1"/>
       <c r="N351" s="1"/>
     </row>
-    <row r="352" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" ht="12.75" customHeight="true">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -6359,7 +6781,7 @@
       <c r="M352" s="1"/>
       <c r="N352" s="1"/>
     </row>
-    <row r="353" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" ht="12.75" customHeight="true">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -6375,7 +6797,7 @@
       <c r="M353" s="1"/>
       <c r="N353" s="1"/>
     </row>
-    <row r="354" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" ht="12.75" customHeight="true">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -6391,7 +6813,7 @@
       <c r="M354" s="1"/>
       <c r="N354" s="1"/>
     </row>
-    <row r="355" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" ht="12.75" customHeight="true">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -6407,7 +6829,7 @@
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
     </row>
-    <row r="356" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" ht="12.75" customHeight="true">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -6423,7 +6845,7 @@
       <c r="M356" s="1"/>
       <c r="N356" s="1"/>
     </row>
-    <row r="357" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" ht="12.75" customHeight="true">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -6439,7 +6861,7 @@
       <c r="M357" s="1"/>
       <c r="N357" s="1"/>
     </row>
-    <row r="358" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" ht="12.75" customHeight="true">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -6455,7 +6877,7 @@
       <c r="M358" s="1"/>
       <c r="N358" s="1"/>
     </row>
-    <row r="359" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" ht="12.75" customHeight="true">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -6471,7 +6893,7 @@
       <c r="M359" s="1"/>
       <c r="N359" s="1"/>
     </row>
-    <row r="360" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" ht="12.75" customHeight="true">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -6487,7 +6909,7 @@
       <c r="M360" s="1"/>
       <c r="N360" s="1"/>
     </row>
-    <row r="361" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" ht="12.75" customHeight="true">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -6503,7 +6925,7 @@
       <c r="M361" s="1"/>
       <c r="N361" s="1"/>
     </row>
-    <row r="362" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" ht="12.75" customHeight="true">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -6519,7 +6941,7 @@
       <c r="M362" s="1"/>
       <c r="N362" s="1"/>
     </row>
-    <row r="363" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" ht="12.75" customHeight="true">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -6535,7 +6957,7 @@
       <c r="M363" s="1"/>
       <c r="N363" s="1"/>
     </row>
-    <row r="364" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" ht="12.75" customHeight="true">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -6551,7 +6973,7 @@
       <c r="M364" s="1"/>
       <c r="N364" s="1"/>
     </row>
-    <row r="365" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" ht="12.75" customHeight="true">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -6567,7 +6989,7 @@
       <c r="M365" s="1"/>
       <c r="N365" s="1"/>
     </row>
-    <row r="366" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" ht="12.75" customHeight="true">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -6583,7 +7005,7 @@
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
     </row>
-    <row r="367" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" ht="12.75" customHeight="true">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -6599,7 +7021,7 @@
       <c r="M367" s="1"/>
       <c r="N367" s="1"/>
     </row>
-    <row r="368" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" ht="12.75" customHeight="true">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -6615,7 +7037,7 @@
       <c r="M368" s="1"/>
       <c r="N368" s="1"/>
     </row>
-    <row r="369" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" ht="12.75" customHeight="true">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -6631,7 +7053,7 @@
       <c r="M369" s="1"/>
       <c r="N369" s="1"/>
     </row>
-    <row r="370" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" ht="12.75" customHeight="true">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -6647,7 +7069,7 @@
       <c r="M370" s="1"/>
       <c r="N370" s="1"/>
     </row>
-    <row r="371" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" ht="12.75" customHeight="true">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -6663,7 +7085,7 @@
       <c r="M371" s="1"/>
       <c r="N371" s="1"/>
     </row>
-    <row r="372" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" ht="12.75" customHeight="true">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -6679,7 +7101,7 @@
       <c r="M372" s="1"/>
       <c r="N372" s="1"/>
     </row>
-    <row r="373" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" ht="12.75" customHeight="true">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -6695,7 +7117,7 @@
       <c r="M373" s="1"/>
       <c r="N373" s="1"/>
     </row>
-    <row r="374" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" ht="12.75" customHeight="true">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -6711,7 +7133,7 @@
       <c r="M374" s="1"/>
       <c r="N374" s="1"/>
     </row>
-    <row r="375" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" ht="12.75" customHeight="true">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -6727,7 +7149,7 @@
       <c r="M375" s="1"/>
       <c r="N375" s="1"/>
     </row>
-    <row r="376" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" ht="12.75" customHeight="true">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -6743,7 +7165,7 @@
       <c r="M376" s="1"/>
       <c r="N376" s="1"/>
     </row>
-    <row r="377" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" ht="12.75" customHeight="true">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -6759,7 +7181,7 @@
       <c r="M377" s="1"/>
       <c r="N377" s="1"/>
     </row>
-    <row r="378" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" ht="12.75" customHeight="true">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -6775,7 +7197,7 @@
       <c r="M378" s="1"/>
       <c r="N378" s="1"/>
     </row>
-    <row r="379" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" ht="12.75" customHeight="true">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -6791,7 +7213,7 @@
       <c r="M379" s="1"/>
       <c r="N379" s="1"/>
     </row>
-    <row r="380" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" ht="12.75" customHeight="true">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -6807,7 +7229,7 @@
       <c r="M380" s="1"/>
       <c r="N380" s="1"/>
     </row>
-    <row r="381" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" ht="12.75" customHeight="true">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -6823,7 +7245,7 @@
       <c r="M381" s="1"/>
       <c r="N381" s="1"/>
     </row>
-    <row r="382" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" ht="12.75" customHeight="true">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -6839,7 +7261,7 @@
       <c r="M382" s="1"/>
       <c r="N382" s="1"/>
     </row>
-    <row r="383" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" ht="12.75" customHeight="true">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -6855,7 +7277,7 @@
       <c r="M383" s="1"/>
       <c r="N383" s="1"/>
     </row>
-    <row r="384" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" ht="12.75" customHeight="true">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -6871,7 +7293,7 @@
       <c r="M384" s="1"/>
       <c r="N384" s="1"/>
     </row>
-    <row r="385" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" ht="12.75" customHeight="true">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -6887,7 +7309,7 @@
       <c r="M385" s="1"/>
       <c r="N385" s="1"/>
     </row>
-    <row r="386" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" ht="12.75" customHeight="true">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -6903,7 +7325,7 @@
       <c r="M386" s="1"/>
       <c r="N386" s="1"/>
     </row>
-    <row r="387" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" ht="12.75" customHeight="true">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -6919,7 +7341,7 @@
       <c r="M387" s="1"/>
       <c r="N387" s="1"/>
     </row>
-    <row r="388" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" ht="12.75" customHeight="true">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -6935,7 +7357,7 @@
       <c r="M388" s="1"/>
       <c r="N388" s="1"/>
     </row>
-    <row r="389" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" ht="12.75" customHeight="true">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -6951,7 +7373,7 @@
       <c r="M389" s="1"/>
       <c r="N389" s="1"/>
     </row>
-    <row r="390" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" ht="12.75" customHeight="true">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -6967,7 +7389,7 @@
       <c r="M390" s="1"/>
       <c r="N390" s="1"/>
     </row>
-    <row r="391" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" ht="12.75" customHeight="true">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -6983,7 +7405,7 @@
       <c r="M391" s="1"/>
       <c r="N391" s="1"/>
     </row>
-    <row r="392" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" ht="12.75" customHeight="true">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -6999,7 +7421,7 @@
       <c r="M392" s="1"/>
       <c r="N392" s="1"/>
     </row>
-    <row r="393" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" ht="12.75" customHeight="true">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -7015,7 +7437,7 @@
       <c r="M393" s="1"/>
       <c r="N393" s="1"/>
     </row>
-    <row r="394" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" ht="12.75" customHeight="true">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -7031,7 +7453,7 @@
       <c r="M394" s="1"/>
       <c r="N394" s="1"/>
     </row>
-    <row r="395" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" ht="12.75" customHeight="true">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -7047,7 +7469,7 @@
       <c r="M395" s="1"/>
       <c r="N395" s="1"/>
     </row>
-    <row r="396" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" ht="12.75" customHeight="true">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -7063,7 +7485,7 @@
       <c r="M396" s="1"/>
       <c r="N396" s="1"/>
     </row>
-    <row r="397" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" ht="12.75" customHeight="true">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -7079,7 +7501,7 @@
       <c r="M397" s="1"/>
       <c r="N397" s="1"/>
     </row>
-    <row r="398" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" ht="12.75" customHeight="true">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -7095,7 +7517,7 @@
       <c r="M398" s="1"/>
       <c r="N398" s="1"/>
     </row>
-    <row r="399" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" ht="12.75" customHeight="true">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -7111,7 +7533,7 @@
       <c r="M399" s="1"/>
       <c r="N399" s="1"/>
     </row>
-    <row r="400" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" ht="12.75" customHeight="true">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -7127,7 +7549,7 @@
       <c r="M400" s="1"/>
       <c r="N400" s="1"/>
     </row>
-    <row r="401" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" ht="12.75" customHeight="true">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -7143,7 +7565,7 @@
       <c r="M401" s="1"/>
       <c r="N401" s="1"/>
     </row>
-    <row r="402" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="402" ht="12.75" customHeight="true">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -7159,7 +7581,7 @@
       <c r="M402" s="1"/>
       <c r="N402" s="1"/>
     </row>
-    <row r="403" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="403" ht="12.75" customHeight="true">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -7175,7 +7597,7 @@
       <c r="M403" s="1"/>
       <c r="N403" s="1"/>
     </row>
-    <row r="404" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="404" ht="12.75" customHeight="true">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -7191,7 +7613,7 @@
       <c r="M404" s="1"/>
       <c r="N404" s="1"/>
     </row>
-    <row r="405" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="405" ht="12.75" customHeight="true">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -7207,7 +7629,7 @@
       <c r="M405" s="1"/>
       <c r="N405" s="1"/>
     </row>
-    <row r="406" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="406" ht="12.75" customHeight="true">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -7223,7 +7645,7 @@
       <c r="M406" s="1"/>
       <c r="N406" s="1"/>
     </row>
-    <row r="407" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="407" ht="12.75" customHeight="true">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -7239,7 +7661,7 @@
       <c r="M407" s="1"/>
       <c r="N407" s="1"/>
     </row>
-    <row r="408" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="408" ht="12.75" customHeight="true">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -7255,7 +7677,7 @@
       <c r="M408" s="1"/>
       <c r="N408" s="1"/>
     </row>
-    <row r="409" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="409" ht="12.75" customHeight="true">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -7271,7 +7693,7 @@
       <c r="M409" s="1"/>
       <c r="N409" s="1"/>
     </row>
-    <row r="410" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="410" ht="12.75" customHeight="true">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -7287,7 +7709,7 @@
       <c r="M410" s="1"/>
       <c r="N410" s="1"/>
     </row>
-    <row r="411" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="411" ht="12.75" customHeight="true">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -7303,7 +7725,7 @@
       <c r="M411" s="1"/>
       <c r="N411" s="1"/>
     </row>
-    <row r="412" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="412" ht="12.75" customHeight="true">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -7319,7 +7741,7 @@
       <c r="M412" s="1"/>
       <c r="N412" s="1"/>
     </row>
-    <row r="413" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="413" ht="12.75" customHeight="true">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -7335,7 +7757,7 @@
       <c r="M413" s="1"/>
       <c r="N413" s="1"/>
     </row>
-    <row r="414" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="414" ht="12.75" customHeight="true">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -7351,7 +7773,7 @@
       <c r="M414" s="1"/>
       <c r="N414" s="1"/>
     </row>
-    <row r="415" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="415" ht="12.75" customHeight="true">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -7367,7 +7789,7 @@
       <c r="M415" s="1"/>
       <c r="N415" s="1"/>
     </row>
-    <row r="416" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="416" ht="12.75" customHeight="true">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -7383,7 +7805,7 @@
       <c r="M416" s="1"/>
       <c r="N416" s="1"/>
     </row>
-    <row r="417" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="417" ht="12.75" customHeight="true">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -7399,7 +7821,7 @@
       <c r="M417" s="1"/>
       <c r="N417" s="1"/>
     </row>
-    <row r="418" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="418" ht="12.75" customHeight="true">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -7415,7 +7837,7 @@
       <c r="M418" s="1"/>
       <c r="N418" s="1"/>
     </row>
-    <row r="419" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="419" ht="12.75" customHeight="true">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -7431,7 +7853,7 @@
       <c r="M419" s="1"/>
       <c r="N419" s="1"/>
     </row>
-    <row r="420" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="420" ht="12.75" customHeight="true">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -7447,7 +7869,7 @@
       <c r="M420" s="1"/>
       <c r="N420" s="1"/>
     </row>
-    <row r="421" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="421" ht="12.75" customHeight="true">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -7463,7 +7885,7 @@
       <c r="M421" s="1"/>
       <c r="N421" s="1"/>
     </row>
-    <row r="422" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="422" ht="12.75" customHeight="true">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -7479,7 +7901,7 @@
       <c r="M422" s="1"/>
       <c r="N422" s="1"/>
     </row>
-    <row r="423" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="423" ht="12.75" customHeight="true">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -7495,7 +7917,7 @@
       <c r="M423" s="1"/>
       <c r="N423" s="1"/>
     </row>
-    <row r="424" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="424" ht="12.75" customHeight="true">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -7511,7 +7933,7 @@
       <c r="M424" s="1"/>
       <c r="N424" s="1"/>
     </row>
-    <row r="425" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="425" ht="12.75" customHeight="true">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -7527,7 +7949,7 @@
       <c r="M425" s="1"/>
       <c r="N425" s="1"/>
     </row>
-    <row r="426" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="426" ht="12.75" customHeight="true">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -7543,7 +7965,7 @@
       <c r="M426" s="1"/>
       <c r="N426" s="1"/>
     </row>
-    <row r="427" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="427" ht="12.75" customHeight="true">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -7559,7 +7981,7 @@
       <c r="M427" s="1"/>
       <c r="N427" s="1"/>
     </row>
-    <row r="428" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="428" ht="12.75" customHeight="true">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -7575,7 +7997,7 @@
       <c r="M428" s="1"/>
       <c r="N428" s="1"/>
     </row>
-    <row r="429" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="429" ht="12.75" customHeight="true">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -7591,7 +8013,7 @@
       <c r="M429" s="1"/>
       <c r="N429" s="1"/>
     </row>
-    <row r="430" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="430" ht="12.75" customHeight="true">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -7607,7 +8029,7 @@
       <c r="M430" s="1"/>
       <c r="N430" s="1"/>
     </row>
-    <row r="431" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="431" ht="12.75" customHeight="true">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -7623,7 +8045,7 @@
       <c r="M431" s="1"/>
       <c r="N431" s="1"/>
     </row>
-    <row r="432" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="432" ht="12.75" customHeight="true">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -7639,7 +8061,7 @@
       <c r="M432" s="1"/>
       <c r="N432" s="1"/>
     </row>
-    <row r="433" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="433" ht="12.75" customHeight="true">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -7655,7 +8077,7 @@
       <c r="M433" s="1"/>
       <c r="N433" s="1"/>
     </row>
-    <row r="434" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="434" ht="12.75" customHeight="true">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -7671,7 +8093,7 @@
       <c r="M434" s="1"/>
       <c r="N434" s="1"/>
     </row>
-    <row r="435" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="435" ht="12.75" customHeight="true">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -7687,7 +8109,7 @@
       <c r="M435" s="1"/>
       <c r="N435" s="1"/>
     </row>
-    <row r="436" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="436" ht="12.75" customHeight="true">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -7703,7 +8125,7 @@
       <c r="M436" s="1"/>
       <c r="N436" s="1"/>
     </row>
-    <row r="437" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="437" ht="12.75" customHeight="true">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -7719,7 +8141,7 @@
       <c r="M437" s="1"/>
       <c r="N437" s="1"/>
     </row>
-    <row r="438" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="438" ht="12.75" customHeight="true">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -7735,7 +8157,7 @@
       <c r="M438" s="1"/>
       <c r="N438" s="1"/>
     </row>
-    <row r="439" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="439" ht="12.75" customHeight="true">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -7751,7 +8173,7 @@
       <c r="M439" s="1"/>
       <c r="N439" s="1"/>
     </row>
-    <row r="440" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="440" ht="12.75" customHeight="true">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -7767,7 +8189,7 @@
       <c r="M440" s="1"/>
       <c r="N440" s="1"/>
     </row>
-    <row r="441" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="441" ht="12.75" customHeight="true">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -7783,7 +8205,7 @@
       <c r="M441" s="1"/>
       <c r="N441" s="1"/>
     </row>
-    <row r="442" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="442" ht="12.75" customHeight="true">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -7799,7 +8221,7 @@
       <c r="M442" s="1"/>
       <c r="N442" s="1"/>
     </row>
-    <row r="443" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="443" ht="12.75" customHeight="true">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -7815,7 +8237,7 @@
       <c r="M443" s="1"/>
       <c r="N443" s="1"/>
     </row>
-    <row r="444" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="444" ht="12.75" customHeight="true">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -7831,7 +8253,7 @@
       <c r="M444" s="1"/>
       <c r="N444" s="1"/>
     </row>
-    <row r="445" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="445" ht="12.75" customHeight="true">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -7847,7 +8269,7 @@
       <c r="M445" s="1"/>
       <c r="N445" s="1"/>
     </row>
-    <row r="446" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="446" ht="12.75" customHeight="true">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -7863,7 +8285,7 @@
       <c r="M446" s="1"/>
       <c r="N446" s="1"/>
     </row>
-    <row r="447" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="447" ht="12.75" customHeight="true">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -7879,7 +8301,7 @@
       <c r="M447" s="1"/>
       <c r="N447" s="1"/>
     </row>
-    <row r="448" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="448" ht="12.75" customHeight="true">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -7895,7 +8317,7 @@
       <c r="M448" s="1"/>
       <c r="N448" s="1"/>
     </row>
-    <row r="449" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="449" ht="12.75" customHeight="true">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -7911,7 +8333,7 @@
       <c r="M449" s="1"/>
       <c r="N449" s="1"/>
     </row>
-    <row r="450" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="450" ht="12.75" customHeight="true">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -7927,7 +8349,7 @@
       <c r="M450" s="1"/>
       <c r="N450" s="1"/>
     </row>
-    <row r="451" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="451" ht="12.75" customHeight="true">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -7943,7 +8365,7 @@
       <c r="M451" s="1"/>
       <c r="N451" s="1"/>
     </row>
-    <row r="452" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="452" ht="12.75" customHeight="true">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -7959,7 +8381,7 @@
       <c r="M452" s="1"/>
       <c r="N452" s="1"/>
     </row>
-    <row r="453" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="453" ht="12.75" customHeight="true">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -7975,7 +8397,7 @@
       <c r="M453" s="1"/>
       <c r="N453" s="1"/>
     </row>
-    <row r="454" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="454" ht="12.75" customHeight="true">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -7991,7 +8413,7 @@
       <c r="M454" s="1"/>
       <c r="N454" s="1"/>
     </row>
-    <row r="455" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="455" ht="12.75" customHeight="true">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -8007,7 +8429,7 @@
       <c r="M455" s="1"/>
       <c r="N455" s="1"/>
     </row>
-    <row r="456" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="456" ht="12.75" customHeight="true">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -8023,7 +8445,7 @@
       <c r="M456" s="1"/>
       <c r="N456" s="1"/>
     </row>
-    <row r="457" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="457" ht="12.75" customHeight="true">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -8039,7 +8461,7 @@
       <c r="M457" s="1"/>
       <c r="N457" s="1"/>
     </row>
-    <row r="458" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="458" ht="12.75" customHeight="true">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -8055,7 +8477,7 @@
       <c r="M458" s="1"/>
       <c r="N458" s="1"/>
     </row>
-    <row r="459" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="459" ht="12.75" customHeight="true">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -8071,7 +8493,7 @@
       <c r="M459" s="1"/>
       <c r="N459" s="1"/>
     </row>
-    <row r="460" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="460" ht="12.75" customHeight="true">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -8087,7 +8509,7 @@
       <c r="M460" s="1"/>
       <c r="N460" s="1"/>
     </row>
-    <row r="461" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="461" ht="12.75" customHeight="true">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -8103,7 +8525,7 @@
       <c r="M461" s="1"/>
       <c r="N461" s="1"/>
     </row>
-    <row r="462" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="462" ht="12.75" customHeight="true">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -8119,7 +8541,7 @@
       <c r="M462" s="1"/>
       <c r="N462" s="1"/>
     </row>
-    <row r="463" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="463" ht="12.75" customHeight="true">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -8135,7 +8557,7 @@
       <c r="M463" s="1"/>
       <c r="N463" s="1"/>
     </row>
-    <row r="464" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="464" ht="12.75" customHeight="true">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -8151,7 +8573,7 @@
       <c r="M464" s="1"/>
       <c r="N464" s="1"/>
     </row>
-    <row r="465" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="465" ht="12.75" customHeight="true">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -8167,7 +8589,7 @@
       <c r="M465" s="1"/>
       <c r="N465" s="1"/>
     </row>
-    <row r="466" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="466" ht="12.75" customHeight="true">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -8183,7 +8605,7 @@
       <c r="M466" s="1"/>
       <c r="N466" s="1"/>
     </row>
-    <row r="467" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="467" ht="12.75" customHeight="true">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -8199,7 +8621,7 @@
       <c r="M467" s="1"/>
       <c r="N467" s="1"/>
     </row>
-    <row r="468" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="468" ht="12.75" customHeight="true">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -8215,7 +8637,7 @@
       <c r="M468" s="1"/>
       <c r="N468" s="1"/>
     </row>
-    <row r="469" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="469" ht="12.75" customHeight="true">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -8231,7 +8653,7 @@
       <c r="M469" s="1"/>
       <c r="N469" s="1"/>
     </row>
-    <row r="470" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="470" ht="12.75" customHeight="true">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -8247,7 +8669,7 @@
       <c r="M470" s="1"/>
       <c r="N470" s="1"/>
     </row>
-    <row r="471" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="471" ht="12.75" customHeight="true">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -8263,7 +8685,7 @@
       <c r="M471" s="1"/>
       <c r="N471" s="1"/>
     </row>
-    <row r="472" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="472" ht="12.75" customHeight="true">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -8279,7 +8701,7 @@
       <c r="M472" s="1"/>
       <c r="N472" s="1"/>
     </row>
-    <row r="473" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="473" ht="12.75" customHeight="true">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -8295,7 +8717,7 @@
       <c r="M473" s="1"/>
       <c r="N473" s="1"/>
     </row>
-    <row r="474" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="474" ht="12.75" customHeight="true">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -8311,7 +8733,7 @@
       <c r="M474" s="1"/>
       <c r="N474" s="1"/>
     </row>
-    <row r="475" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="475" ht="12.75" customHeight="true">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -8327,7 +8749,7 @@
       <c r="M475" s="1"/>
       <c r="N475" s="1"/>
     </row>
-    <row r="476" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="476" ht="12.75" customHeight="true">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -8343,7 +8765,7 @@
       <c r="M476" s="1"/>
       <c r="N476" s="1"/>
     </row>
-    <row r="477" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="477" ht="12.75" customHeight="true">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -8359,7 +8781,7 @@
       <c r="M477" s="1"/>
       <c r="N477" s="1"/>
     </row>
-    <row r="478" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="478" ht="12.75" customHeight="true">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -8375,7 +8797,7 @@
       <c r="M478" s="1"/>
       <c r="N478" s="1"/>
     </row>
-    <row r="479" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="479" ht="12.75" customHeight="true">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -8391,7 +8813,7 @@
       <c r="M479" s="1"/>
       <c r="N479" s="1"/>
     </row>
-    <row r="480" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="480" ht="12.75" customHeight="true">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -8407,7 +8829,7 @@
       <c r="M480" s="1"/>
       <c r="N480" s="1"/>
     </row>
-    <row r="481" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="481" ht="12.75" customHeight="true">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -8423,7 +8845,7 @@
       <c r="M481" s="1"/>
       <c r="N481" s="1"/>
     </row>
-    <row r="482" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="482" ht="12.75" customHeight="true">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -8439,7 +8861,7 @@
       <c r="M482" s="1"/>
       <c r="N482" s="1"/>
     </row>
-    <row r="483" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="483" ht="12.75" customHeight="true">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -8455,7 +8877,7 @@
       <c r="M483" s="1"/>
       <c r="N483" s="1"/>
     </row>
-    <row r="484" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="484" ht="12.75" customHeight="true">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -8471,7 +8893,7 @@
       <c r="M484" s="1"/>
       <c r="N484" s="1"/>
     </row>
-    <row r="485" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="485" ht="12.75" customHeight="true">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -8487,7 +8909,7 @@
       <c r="M485" s="1"/>
       <c r="N485" s="1"/>
     </row>
-    <row r="486" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="486" ht="12.75" customHeight="true">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -8503,7 +8925,7 @@
       <c r="M486" s="1"/>
       <c r="N486" s="1"/>
     </row>
-    <row r="487" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="487" ht="12.75" customHeight="true">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -8519,7 +8941,7 @@
       <c r="M487" s="1"/>
       <c r="N487" s="1"/>
     </row>
-    <row r="488" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="488" ht="12.75" customHeight="true">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -8535,7 +8957,7 @@
       <c r="M488" s="1"/>
       <c r="N488" s="1"/>
     </row>
-    <row r="489" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="489" ht="12.75" customHeight="true">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -8551,7 +8973,7 @@
       <c r="M489" s="1"/>
       <c r="N489" s="1"/>
     </row>
-    <row r="490" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="490" ht="12.75" customHeight="true">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -8567,7 +8989,7 @@
       <c r="M490" s="1"/>
       <c r="N490" s="1"/>
     </row>
-    <row r="491" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="491" ht="12.75" customHeight="true">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -8583,7 +9005,7 @@
       <c r="M491" s="1"/>
       <c r="N491" s="1"/>
     </row>
-    <row r="492" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="492" ht="12.75" customHeight="true">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -8599,7 +9021,7 @@
       <c r="M492" s="1"/>
       <c r="N492" s="1"/>
     </row>
-    <row r="493" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="493" ht="12.75" customHeight="true">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -8615,7 +9037,7 @@
       <c r="M493" s="1"/>
       <c r="N493" s="1"/>
     </row>
-    <row r="494" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="494" ht="12.75" customHeight="true">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -8631,7 +9053,7 @@
       <c r="M494" s="1"/>
       <c r="N494" s="1"/>
     </row>
-    <row r="495" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="495" ht="12.75" customHeight="true">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -8647,7 +9069,7 @@
       <c r="M495" s="1"/>
       <c r="N495" s="1"/>
     </row>
-    <row r="496" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="496" ht="12.75" customHeight="true">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -8663,7 +9085,7 @@
       <c r="M496" s="1"/>
       <c r="N496" s="1"/>
     </row>
-    <row r="497" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="497" ht="12.75" customHeight="true">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -8679,7 +9101,7 @@
       <c r="M497" s="1"/>
       <c r="N497" s="1"/>
     </row>
-    <row r="498" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="498" ht="12.75" customHeight="true">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -8695,7 +9117,7 @@
       <c r="M498" s="1"/>
       <c r="N498" s="1"/>
     </row>
-    <row r="499" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="499" ht="12.75" customHeight="true">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -8711,7 +9133,7 @@
       <c r="M499" s="1"/>
       <c r="N499" s="1"/>
     </row>
-    <row r="500" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="500" ht="12.75" customHeight="true">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -8727,7 +9149,7 @@
       <c r="M500" s="1"/>
       <c r="N500" s="1"/>
     </row>
-    <row r="501" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="501" ht="12.75" customHeight="true">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -8743,7 +9165,7 @@
       <c r="M501" s="1"/>
       <c r="N501" s="1"/>
     </row>
-    <row r="502" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="502" ht="12.75" customHeight="true">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -8759,7 +9181,7 @@
       <c r="M502" s="1"/>
       <c r="N502" s="1"/>
     </row>
-    <row r="503" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="503" ht="12.75" customHeight="true">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -8775,7 +9197,7 @@
       <c r="M503" s="1"/>
       <c r="N503" s="1"/>
     </row>
-    <row r="504" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="504" ht="12.75" customHeight="true">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -8791,7 +9213,7 @@
       <c r="M504" s="1"/>
       <c r="N504" s="1"/>
     </row>
-    <row r="505" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="505" ht="12.75" customHeight="true">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -8807,7 +9229,7 @@
       <c r="M505" s="1"/>
       <c r="N505" s="1"/>
     </row>
-    <row r="506" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="506" ht="12.75" customHeight="true">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -8823,7 +9245,7 @@
       <c r="M506" s="1"/>
       <c r="N506" s="1"/>
     </row>
-    <row r="507" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="507" ht="12.75" customHeight="true">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -8839,7 +9261,7 @@
       <c r="M507" s="1"/>
       <c r="N507" s="1"/>
     </row>
-    <row r="508" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="508" ht="12.75" customHeight="true">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -8855,7 +9277,7 @@
       <c r="M508" s="1"/>
       <c r="N508" s="1"/>
     </row>
-    <row r="509" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="509" ht="12.75" customHeight="true">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -8871,7 +9293,7 @@
       <c r="M509" s="1"/>
       <c r="N509" s="1"/>
     </row>
-    <row r="510" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="510" ht="12.75" customHeight="true">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -8887,7 +9309,7 @@
       <c r="M510" s="1"/>
       <c r="N510" s="1"/>
     </row>
-    <row r="511" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="511" ht="12.75" customHeight="true">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -8903,7 +9325,7 @@
       <c r="M511" s="1"/>
       <c r="N511" s="1"/>
     </row>
-    <row r="512" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="512" ht="12.75" customHeight="true">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -8919,7 +9341,7 @@
       <c r="M512" s="1"/>
       <c r="N512" s="1"/>
     </row>
-    <row r="513" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="513" ht="12.75" customHeight="true">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -8935,7 +9357,7 @@
       <c r="M513" s="1"/>
       <c r="N513" s="1"/>
     </row>
-    <row r="514" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="514" ht="12.75" customHeight="true">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -8951,7 +9373,7 @@
       <c r="M514" s="1"/>
       <c r="N514" s="1"/>
     </row>
-    <row r="515" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="515" ht="12.75" customHeight="true">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -8967,7 +9389,7 @@
       <c r="M515" s="1"/>
       <c r="N515" s="1"/>
     </row>
-    <row r="516" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="516" ht="12.75" customHeight="true">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -8983,7 +9405,7 @@
       <c r="M516" s="1"/>
       <c r="N516" s="1"/>
     </row>
-    <row r="517" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="517" ht="12.75" customHeight="true">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -8999,7 +9421,7 @@
       <c r="M517" s="1"/>
       <c r="N517" s="1"/>
     </row>
-    <row r="518" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="518" ht="12.75" customHeight="true">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -9015,7 +9437,7 @@
       <c r="M518" s="1"/>
       <c r="N518" s="1"/>
     </row>
-    <row r="519" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="519" ht="12.75" customHeight="true">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -9031,7 +9453,7 @@
       <c r="M519" s="1"/>
       <c r="N519" s="1"/>
     </row>
-    <row r="520" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="520" ht="12.75" customHeight="true">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -9047,7 +9469,7 @@
       <c r="M520" s="1"/>
       <c r="N520" s="1"/>
     </row>
-    <row r="521" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="521" ht="12.75" customHeight="true">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -9063,7 +9485,7 @@
       <c r="M521" s="1"/>
       <c r="N521" s="1"/>
     </row>
-    <row r="522" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="522" ht="12.75" customHeight="true">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -9079,7 +9501,7 @@
       <c r="M522" s="1"/>
       <c r="N522" s="1"/>
     </row>
-    <row r="523" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="523" ht="12.75" customHeight="true">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -9095,7 +9517,7 @@
       <c r="M523" s="1"/>
       <c r="N523" s="1"/>
     </row>
-    <row r="524" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="524" ht="12.75" customHeight="true">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -9111,7 +9533,7 @@
       <c r="M524" s="1"/>
       <c r="N524" s="1"/>
     </row>
-    <row r="525" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="525" ht="12.75" customHeight="true">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -9127,7 +9549,7 @@
       <c r="M525" s="1"/>
       <c r="N525" s="1"/>
     </row>
-    <row r="526" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="526" ht="12.75" customHeight="true">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -9143,7 +9565,7 @@
       <c r="M526" s="1"/>
       <c r="N526" s="1"/>
     </row>
-    <row r="527" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="527" ht="12.75" customHeight="true">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -9159,7 +9581,7 @@
       <c r="M527" s="1"/>
       <c r="N527" s="1"/>
     </row>
-    <row r="528" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="528" ht="12.75" customHeight="true">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -9175,7 +9597,7 @@
       <c r="M528" s="1"/>
       <c r="N528" s="1"/>
     </row>
-    <row r="529" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="529" ht="12.75" customHeight="true">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -9191,7 +9613,7 @@
       <c r="M529" s="1"/>
       <c r="N529" s="1"/>
     </row>
-    <row r="530" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="530" ht="12.75" customHeight="true">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -9207,7 +9629,7 @@
       <c r="M530" s="1"/>
       <c r="N530" s="1"/>
     </row>
-    <row r="531" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="531" ht="12.75" customHeight="true">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -9223,7 +9645,7 @@
       <c r="M531" s="1"/>
       <c r="N531" s="1"/>
     </row>
-    <row r="532" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="532" ht="12.75" customHeight="true">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -9239,7 +9661,7 @@
       <c r="M532" s="1"/>
       <c r="N532" s="1"/>
     </row>
-    <row r="533" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="533" ht="12.75" customHeight="true">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -9255,7 +9677,7 @@
       <c r="M533" s="1"/>
       <c r="N533" s="1"/>
     </row>
-    <row r="534" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="534" ht="12.75" customHeight="true">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -9271,7 +9693,7 @@
       <c r="M534" s="1"/>
       <c r="N534" s="1"/>
     </row>
-    <row r="535" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="535" ht="12.75" customHeight="true">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -9287,7 +9709,7 @@
       <c r="M535" s="1"/>
       <c r="N535" s="1"/>
     </row>
-    <row r="536" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="536" ht="12.75" customHeight="true">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -9303,7 +9725,7 @@
       <c r="M536" s="1"/>
       <c r="N536" s="1"/>
     </row>
-    <row r="537" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="537" ht="12.75" customHeight="true">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -9319,7 +9741,7 @@
       <c r="M537" s="1"/>
       <c r="N537" s="1"/>
     </row>
-    <row r="538" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="538" ht="12.75" customHeight="true">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -9335,7 +9757,7 @@
       <c r="M538" s="1"/>
       <c r="N538" s="1"/>
     </row>
-    <row r="539" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="539" ht="12.75" customHeight="true">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -9351,7 +9773,7 @@
       <c r="M539" s="1"/>
       <c r="N539" s="1"/>
     </row>
-    <row r="540" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="540" ht="12.75" customHeight="true">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -9367,7 +9789,7 @@
       <c r="M540" s="1"/>
       <c r="N540" s="1"/>
     </row>
-    <row r="541" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="541" ht="12.75" customHeight="true">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -9383,7 +9805,7 @@
       <c r="M541" s="1"/>
       <c r="N541" s="1"/>
     </row>
-    <row r="542" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="542" ht="12.75" customHeight="true">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -9399,7 +9821,7 @@
       <c r="M542" s="1"/>
       <c r="N542" s="1"/>
     </row>
-    <row r="543" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="543" ht="12.75" customHeight="true">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -9415,7 +9837,7 @@
       <c r="M543" s="1"/>
       <c r="N543" s="1"/>
     </row>
-    <row r="544" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="544" ht="12.75" customHeight="true">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -9431,7 +9853,7 @@
       <c r="M544" s="1"/>
       <c r="N544" s="1"/>
     </row>
-    <row r="545" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="545" ht="12.75" customHeight="true">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -9447,7 +9869,7 @@
       <c r="M545" s="1"/>
       <c r="N545" s="1"/>
     </row>
-    <row r="546" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="546" ht="12.75" customHeight="true">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -9463,7 +9885,7 @@
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
     </row>
-    <row r="547" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="547" ht="12.75" customHeight="true">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -9479,7 +9901,7 @@
       <c r="M547" s="1"/>
       <c r="N547" s="1"/>
     </row>
-    <row r="548" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="548" ht="12.75" customHeight="true">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -9495,7 +9917,7 @@
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
     </row>
-    <row r="549" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="549" ht="12.75" customHeight="true">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -9511,7 +9933,7 @@
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
     </row>
-    <row r="550" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="550" ht="12.75" customHeight="true">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -9527,7 +9949,7 @@
       <c r="M550" s="1"/>
       <c r="N550" s="1"/>
     </row>
-    <row r="551" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="551" ht="12.75" customHeight="true">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -9543,7 +9965,7 @@
       <c r="M551" s="1"/>
       <c r="N551" s="1"/>
     </row>
-    <row r="552" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="552" ht="12.75" customHeight="true">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -9559,7 +9981,7 @@
       <c r="M552" s="1"/>
       <c r="N552" s="1"/>
     </row>
-    <row r="553" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="553" ht="12.75" customHeight="true">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -9575,7 +9997,7 @@
       <c r="M553" s="1"/>
       <c r="N553" s="1"/>
     </row>
-    <row r="554" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="554" ht="12.75" customHeight="true">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -9591,7 +10013,7 @@
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
     </row>
-    <row r="555" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="555" ht="12.75" customHeight="true">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -9607,7 +10029,7 @@
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
     </row>
-    <row r="556" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="556" ht="12.75" customHeight="true">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -9623,7 +10045,7 @@
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
     </row>
-    <row r="557" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="557" ht="12.75" customHeight="true">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -9639,7 +10061,7 @@
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
     </row>
-    <row r="558" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="558" ht="12.75" customHeight="true">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -9655,7 +10077,7 @@
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
     </row>
-    <row r="559" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="559" ht="12.75" customHeight="true">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -9671,7 +10093,7 @@
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
     </row>
-    <row r="560" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="560" ht="12.75" customHeight="true">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -9687,7 +10109,7 @@
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
     </row>
-    <row r="561" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="561" ht="12.75" customHeight="true">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -9703,7 +10125,7 @@
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
     </row>
-    <row r="562" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="562" ht="12.75" customHeight="true">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -9719,7 +10141,7 @@
       <c r="M562" s="1"/>
       <c r="N562" s="1"/>
     </row>
-    <row r="563" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="563" ht="12.75" customHeight="true">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -9735,7 +10157,7 @@
       <c r="M563" s="1"/>
       <c r="N563" s="1"/>
     </row>
-    <row r="564" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="564" ht="12.75" customHeight="true">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -9751,7 +10173,7 @@
       <c r="M564" s="1"/>
       <c r="N564" s="1"/>
     </row>
-    <row r="565" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="565" ht="12.75" customHeight="true">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -9767,7 +10189,7 @@
       <c r="M565" s="1"/>
       <c r="N565" s="1"/>
     </row>
-    <row r="566" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="566" ht="12.75" customHeight="true">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -9783,7 +10205,7 @@
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
     </row>
-    <row r="567" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="567" ht="12.75" customHeight="true">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -9799,7 +10221,7 @@
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
     </row>
-    <row r="568" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="568" ht="12.75" customHeight="true">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -9815,7 +10237,7 @@
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
     </row>
-    <row r="569" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="569" ht="12.75" customHeight="true">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -9831,7 +10253,7 @@
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
     </row>
-    <row r="570" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="570" ht="12.75" customHeight="true">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -9847,7 +10269,7 @@
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
     </row>
-    <row r="571" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="571" ht="12.75" customHeight="true">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -9863,7 +10285,7 @@
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
     </row>
-    <row r="572" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="572" ht="12.75" customHeight="true">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -9879,7 +10301,7 @@
       <c r="M572" s="1"/>
       <c r="N572" s="1"/>
     </row>
-    <row r="573" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="573" ht="12.75" customHeight="true">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -9895,7 +10317,7 @@
       <c r="M573" s="1"/>
       <c r="N573" s="1"/>
     </row>
-    <row r="574" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="574" ht="12.75" customHeight="true">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -9911,7 +10333,7 @@
       <c r="M574" s="1"/>
       <c r="N574" s="1"/>
     </row>
-    <row r="575" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="575" ht="12.75" customHeight="true">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -9927,7 +10349,7 @@
       <c r="M575" s="1"/>
       <c r="N575" s="1"/>
     </row>
-    <row r="576" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="576" ht="12.75" customHeight="true">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -9943,7 +10365,7 @@
       <c r="M576" s="1"/>
       <c r="N576" s="1"/>
     </row>
-    <row r="577" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="577" ht="12.75" customHeight="true">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -9959,7 +10381,7 @@
       <c r="M577" s="1"/>
       <c r="N577" s="1"/>
     </row>
-    <row r="578" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="578" ht="12.75" customHeight="true">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -9975,7 +10397,7 @@
       <c r="M578" s="1"/>
       <c r="N578" s="1"/>
     </row>
-    <row r="579" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="579" ht="12.75" customHeight="true">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -9991,7 +10413,7 @@
       <c r="M579" s="1"/>
       <c r="N579" s="1"/>
     </row>
-    <row r="580" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="580" ht="12.75" customHeight="true">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -10007,7 +10429,7 @@
       <c r="M580" s="1"/>
       <c r="N580" s="1"/>
     </row>
-    <row r="581" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="581" ht="12.75" customHeight="true">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -10023,7 +10445,7 @@
       <c r="M581" s="1"/>
       <c r="N581" s="1"/>
     </row>
-    <row r="582" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="582" ht="12.75" customHeight="true">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -10039,7 +10461,7 @@
       <c r="M582" s="1"/>
       <c r="N582" s="1"/>
     </row>
-    <row r="583" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="583" ht="12.75" customHeight="true">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -10055,7 +10477,7 @@
       <c r="M583" s="1"/>
       <c r="N583" s="1"/>
     </row>
-    <row r="584" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="584" ht="12.75" customHeight="true">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -10071,7 +10493,7 @@
       <c r="M584" s="1"/>
       <c r="N584" s="1"/>
     </row>
-    <row r="585" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="585" ht="12.75" customHeight="true">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -10087,7 +10509,7 @@
       <c r="M585" s="1"/>
       <c r="N585" s="1"/>
     </row>
-    <row r="586" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="586" ht="12.75" customHeight="true">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -10103,7 +10525,7 @@
       <c r="M586" s="1"/>
       <c r="N586" s="1"/>
     </row>
-    <row r="587" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="587" ht="12.75" customHeight="true">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -10119,7 +10541,7 @@
       <c r="M587" s="1"/>
       <c r="N587" s="1"/>
     </row>
-    <row r="588" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="588" ht="12.75" customHeight="true">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -10135,7 +10557,7 @@
       <c r="M588" s="1"/>
       <c r="N588" s="1"/>
     </row>
-    <row r="589" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="589" ht="12.75" customHeight="true">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -10151,7 +10573,7 @@
       <c r="M589" s="1"/>
       <c r="N589" s="1"/>
     </row>
-    <row r="590" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="590" ht="12.75" customHeight="true">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -10167,7 +10589,7 @@
       <c r="M590" s="1"/>
       <c r="N590" s="1"/>
     </row>
-    <row r="591" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="591" ht="12.75" customHeight="true">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -10183,7 +10605,7 @@
       <c r="M591" s="1"/>
       <c r="N591" s="1"/>
     </row>
-    <row r="592" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="592" ht="12.75" customHeight="true">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -10199,7 +10621,7 @@
       <c r="M592" s="1"/>
       <c r="N592" s="1"/>
     </row>
-    <row r="593" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="593" ht="12.75" customHeight="true">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -10215,7 +10637,7 @@
       <c r="M593" s="1"/>
       <c r="N593" s="1"/>
     </row>
-    <row r="594" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="594" ht="12.75" customHeight="true">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -10231,7 +10653,7 @@
       <c r="M594" s="1"/>
       <c r="N594" s="1"/>
     </row>
-    <row r="595" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="595" ht="12.75" customHeight="true">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -10247,7 +10669,7 @@
       <c r="M595" s="1"/>
       <c r="N595" s="1"/>
     </row>
-    <row r="596" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="596" ht="12.75" customHeight="true">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -10263,7 +10685,7 @@
       <c r="M596" s="1"/>
       <c r="N596" s="1"/>
     </row>
-    <row r="597" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="597" ht="12.75" customHeight="true">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -10279,7 +10701,7 @@
       <c r="M597" s="1"/>
       <c r="N597" s="1"/>
     </row>
-    <row r="598" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="598" ht="12.75" customHeight="true">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -10295,7 +10717,7 @@
       <c r="M598" s="1"/>
       <c r="N598" s="1"/>
     </row>
-    <row r="599" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="599" ht="12.75" customHeight="true">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -10311,7 +10733,7 @@
       <c r="M599" s="1"/>
       <c r="N599" s="1"/>
     </row>
-    <row r="600" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="600" ht="12.75" customHeight="true">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -10327,7 +10749,7 @@
       <c r="M600" s="1"/>
       <c r="N600" s="1"/>
     </row>
-    <row r="601" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="601" ht="12.75" customHeight="true">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -10343,7 +10765,7 @@
       <c r="M601" s="1"/>
       <c r="N601" s="1"/>
     </row>
-    <row r="602" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="602" ht="12.75" customHeight="true">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -10359,7 +10781,7 @@
       <c r="M602" s="1"/>
       <c r="N602" s="1"/>
     </row>
-    <row r="603" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="603" ht="12.75" customHeight="true">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -10375,7 +10797,7 @@
       <c r="M603" s="1"/>
       <c r="N603" s="1"/>
     </row>
-    <row r="604" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="604" ht="12.75" customHeight="true">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -10391,7 +10813,7 @@
       <c r="M604" s="1"/>
       <c r="N604" s="1"/>
     </row>
-    <row r="605" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="605" ht="12.75" customHeight="true">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -10407,7 +10829,7 @@
       <c r="M605" s="1"/>
       <c r="N605" s="1"/>
     </row>
-    <row r="606" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="606" ht="12.75" customHeight="true">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -10423,7 +10845,7 @@
       <c r="M606" s="1"/>
       <c r="N606" s="1"/>
     </row>
-    <row r="607" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="607" ht="12.75" customHeight="true">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -10439,7 +10861,7 @@
       <c r="M607" s="1"/>
       <c r="N607" s="1"/>
     </row>
-    <row r="608" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="608" ht="12.75" customHeight="true">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -10455,7 +10877,7 @@
       <c r="M608" s="1"/>
       <c r="N608" s="1"/>
     </row>
-    <row r="609" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="609" ht="12.75" customHeight="true">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -10471,7 +10893,7 @@
       <c r="M609" s="1"/>
       <c r="N609" s="1"/>
     </row>
-    <row r="610" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="610" ht="12.75" customHeight="true">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -10487,7 +10909,7 @@
       <c r="M610" s="1"/>
       <c r="N610" s="1"/>
     </row>
-    <row r="611" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="611" ht="12.75" customHeight="true">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -10503,7 +10925,7 @@
       <c r="M611" s="1"/>
       <c r="N611" s="1"/>
     </row>
-    <row r="612" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="612" ht="12.75" customHeight="true">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -10519,7 +10941,7 @@
       <c r="M612" s="1"/>
       <c r="N612" s="1"/>
     </row>
-    <row r="613" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="613" ht="12.75" customHeight="true">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -10535,7 +10957,7 @@
       <c r="M613" s="1"/>
       <c r="N613" s="1"/>
     </row>
-    <row r="614" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="614" ht="12.75" customHeight="true">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -10551,7 +10973,7 @@
       <c r="M614" s="1"/>
       <c r="N614" s="1"/>
     </row>
-    <row r="615" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="615" ht="12.75" customHeight="true">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -10567,7 +10989,7 @@
       <c r="M615" s="1"/>
       <c r="N615" s="1"/>
     </row>
-    <row r="616" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="616" ht="12.75" customHeight="true">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -10583,7 +11005,7 @@
       <c r="M616" s="1"/>
       <c r="N616" s="1"/>
     </row>
-    <row r="617" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="617" ht="12.75" customHeight="true">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -10599,7 +11021,7 @@
       <c r="M617" s="1"/>
       <c r="N617" s="1"/>
     </row>
-    <row r="618" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="618" ht="12.75" customHeight="true">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -10615,7 +11037,7 @@
       <c r="M618" s="1"/>
       <c r="N618" s="1"/>
     </row>
-    <row r="619" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="619" ht="12.75" customHeight="true">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -10631,7 +11053,7 @@
       <c r="M619" s="1"/>
       <c r="N619" s="1"/>
     </row>
-    <row r="620" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="620" ht="12.75" customHeight="true">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -10647,7 +11069,7 @@
       <c r="M620" s="1"/>
       <c r="N620" s="1"/>
     </row>
-    <row r="621" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="621" ht="12.75" customHeight="true">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -10663,7 +11085,7 @@
       <c r="M621" s="1"/>
       <c r="N621" s="1"/>
     </row>
-    <row r="622" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="622" ht="12.75" customHeight="true">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -10679,7 +11101,7 @@
       <c r="M622" s="1"/>
       <c r="N622" s="1"/>
     </row>
-    <row r="623" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="623" ht="12.75" customHeight="true">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -10695,7 +11117,7 @@
       <c r="M623" s="1"/>
       <c r="N623" s="1"/>
     </row>
-    <row r="624" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="624" ht="12.75" customHeight="true">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -10711,7 +11133,7 @@
       <c r="M624" s="1"/>
       <c r="N624" s="1"/>
     </row>
-    <row r="625" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="625" ht="12.75" customHeight="true">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -10727,7 +11149,7 @@
       <c r="M625" s="1"/>
       <c r="N625" s="1"/>
     </row>
-    <row r="626" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="626" ht="12.75" customHeight="true">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -10743,7 +11165,7 @@
       <c r="M626" s="1"/>
       <c r="N626" s="1"/>
     </row>
-    <row r="627" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="627" ht="12.75" customHeight="true">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -10759,7 +11181,7 @@
       <c r="M627" s="1"/>
       <c r="N627" s="1"/>
     </row>
-    <row r="628" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="628" ht="12.75" customHeight="true">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -10775,7 +11197,7 @@
       <c r="M628" s="1"/>
       <c r="N628" s="1"/>
     </row>
-    <row r="629" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="629" ht="12.75" customHeight="true">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -10791,7 +11213,7 @@
       <c r="M629" s="1"/>
       <c r="N629" s="1"/>
     </row>
-    <row r="630" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="630" ht="12.75" customHeight="true">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -10807,7 +11229,7 @@
       <c r="M630" s="1"/>
       <c r="N630" s="1"/>
     </row>
-    <row r="631" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="631" ht="12.75" customHeight="true">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -10823,7 +11245,7 @@
       <c r="M631" s="1"/>
       <c r="N631" s="1"/>
     </row>
-    <row r="632" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="632" ht="12.75" customHeight="true">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -10839,7 +11261,7 @@
       <c r="M632" s="1"/>
       <c r="N632" s="1"/>
     </row>
-    <row r="633" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="633" ht="12.75" customHeight="true">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -10855,7 +11277,7 @@
       <c r="M633" s="1"/>
       <c r="N633" s="1"/>
     </row>
-    <row r="634" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="634" ht="12.75" customHeight="true">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -10871,7 +11293,7 @@
       <c r="M634" s="1"/>
       <c r="N634" s="1"/>
     </row>
-    <row r="635" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="635" ht="12.75" customHeight="true">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -10887,7 +11309,7 @@
       <c r="M635" s="1"/>
       <c r="N635" s="1"/>
     </row>
-    <row r="636" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="636" ht="12.75" customHeight="true">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -10903,7 +11325,7 @@
       <c r="M636" s="1"/>
       <c r="N636" s="1"/>
     </row>
-    <row r="637" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="637" ht="12.75" customHeight="true">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -10919,7 +11341,7 @@
       <c r="M637" s="1"/>
       <c r="N637" s="1"/>
     </row>
-    <row r="638" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="638" ht="12.75" customHeight="true">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -10935,7 +11357,7 @@
       <c r="M638" s="1"/>
       <c r="N638" s="1"/>
     </row>
-    <row r="639" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="639" ht="12.75" customHeight="true">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -10951,7 +11373,7 @@
       <c r="M639" s="1"/>
       <c r="N639" s="1"/>
     </row>
-    <row r="640" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="640" ht="12.75" customHeight="true">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -10967,7 +11389,7 @@
       <c r="M640" s="1"/>
       <c r="N640" s="1"/>
     </row>
-    <row r="641" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="641" ht="12.75" customHeight="true">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -10983,7 +11405,7 @@
       <c r="M641" s="1"/>
       <c r="N641" s="1"/>
     </row>
-    <row r="642" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="642" ht="12.75" customHeight="true">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -10999,7 +11421,7 @@
       <c r="M642" s="1"/>
       <c r="N642" s="1"/>
     </row>
-    <row r="643" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="643" ht="12.75" customHeight="true">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -11015,7 +11437,7 @@
       <c r="M643" s="1"/>
       <c r="N643" s="1"/>
     </row>
-    <row r="644" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="644" ht="12.75" customHeight="true">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -11031,7 +11453,7 @@
       <c r="M644" s="1"/>
       <c r="N644" s="1"/>
     </row>
-    <row r="645" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="645" ht="12.75" customHeight="true">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -11047,7 +11469,7 @@
       <c r="M645" s="1"/>
       <c r="N645" s="1"/>
     </row>
-    <row r="646" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="646" ht="12.75" customHeight="true">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -11063,7 +11485,7 @@
       <c r="M646" s="1"/>
       <c r="N646" s="1"/>
     </row>
-    <row r="647" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="647" ht="12.75" customHeight="true">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -11079,7 +11501,7 @@
       <c r="M647" s="1"/>
       <c r="N647" s="1"/>
     </row>
-    <row r="648" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="648" ht="12.75" customHeight="true">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -11095,7 +11517,7 @@
       <c r="M648" s="1"/>
       <c r="N648" s="1"/>
     </row>
-    <row r="649" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="649" ht="12.75" customHeight="true">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -11111,7 +11533,7 @@
       <c r="M649" s="1"/>
       <c r="N649" s="1"/>
     </row>
-    <row r="650" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="650" ht="12.75" customHeight="true">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -11127,7 +11549,7 @@
       <c r="M650" s="1"/>
       <c r="N650" s="1"/>
     </row>
-    <row r="651" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="651" ht="12.75" customHeight="true">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -11143,7 +11565,7 @@
       <c r="M651" s="1"/>
       <c r="N651" s="1"/>
     </row>
-    <row r="652" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="652" ht="12.75" customHeight="true">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -11159,7 +11581,7 @@
       <c r="M652" s="1"/>
       <c r="N652" s="1"/>
     </row>
-    <row r="653" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="653" ht="12.75" customHeight="true">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -11175,7 +11597,7 @@
       <c r="M653" s="1"/>
       <c r="N653" s="1"/>
     </row>
-    <row r="654" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="654" ht="12.75" customHeight="true">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -11191,7 +11613,7 @@
       <c r="M654" s="1"/>
       <c r="N654" s="1"/>
     </row>
-    <row r="655" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="655" ht="12.75" customHeight="true">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -11207,7 +11629,7 @@
       <c r="M655" s="1"/>
       <c r="N655" s="1"/>
     </row>
-    <row r="656" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="656" ht="12.75" customHeight="true">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -11223,7 +11645,7 @@
       <c r="M656" s="1"/>
       <c r="N656" s="1"/>
     </row>
-    <row r="657" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="657" ht="12.75" customHeight="true">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -11239,7 +11661,7 @@
       <c r="M657" s="1"/>
       <c r="N657" s="1"/>
     </row>
-    <row r="658" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="658" ht="12.75" customHeight="true">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -11255,7 +11677,7 @@
       <c r="M658" s="1"/>
       <c r="N658" s="1"/>
     </row>
-    <row r="659" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="659" ht="12.75" customHeight="true">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -11271,7 +11693,7 @@
       <c r="M659" s="1"/>
       <c r="N659" s="1"/>
     </row>
-    <row r="660" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="660" ht="12.75" customHeight="true">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -11287,7 +11709,7 @@
       <c r="M660" s="1"/>
       <c r="N660" s="1"/>
     </row>
-    <row r="661" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="661" ht="12.75" customHeight="true">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -11303,7 +11725,7 @@
       <c r="M661" s="1"/>
       <c r="N661" s="1"/>
     </row>
-    <row r="662" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="662" ht="12.75" customHeight="true">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -11319,7 +11741,7 @@
       <c r="M662" s="1"/>
       <c r="N662" s="1"/>
     </row>
-    <row r="663" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="663" ht="12.75" customHeight="true">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -11335,7 +11757,7 @@
       <c r="M663" s="1"/>
       <c r="N663" s="1"/>
     </row>
-    <row r="664" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="664" ht="12.75" customHeight="true">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -11351,7 +11773,7 @@
       <c r="M664" s="1"/>
       <c r="N664" s="1"/>
     </row>
-    <row r="665" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="665" ht="12.75" customHeight="true">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -11367,7 +11789,7 @@
       <c r="M665" s="1"/>
       <c r="N665" s="1"/>
     </row>
-    <row r="666" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="666" ht="12.75" customHeight="true">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -11383,7 +11805,7 @@
       <c r="M666" s="1"/>
       <c r="N666" s="1"/>
     </row>
-    <row r="667" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="667" ht="12.75" customHeight="true">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -11399,7 +11821,7 @@
       <c r="M667" s="1"/>
       <c r="N667" s="1"/>
     </row>
-    <row r="668" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="668" ht="12.75" customHeight="true">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -11415,7 +11837,7 @@
       <c r="M668" s="1"/>
       <c r="N668" s="1"/>
     </row>
-    <row r="669" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="669" ht="12.75" customHeight="true">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -11431,7 +11853,7 @@
       <c r="M669" s="1"/>
       <c r="N669" s="1"/>
     </row>
-    <row r="670" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="670" ht="12.75" customHeight="true">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -11447,7 +11869,7 @@
       <c r="M670" s="1"/>
       <c r="N670" s="1"/>
     </row>
-    <row r="671" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="671" ht="12.75" customHeight="true">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -11463,7 +11885,7 @@
       <c r="M671" s="1"/>
       <c r="N671" s="1"/>
     </row>
-    <row r="672" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="672" ht="12.75" customHeight="true">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -11479,7 +11901,7 @@
       <c r="M672" s="1"/>
       <c r="N672" s="1"/>
     </row>
-    <row r="673" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="673" ht="12.75" customHeight="true">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -11495,7 +11917,7 @@
       <c r="M673" s="1"/>
       <c r="N673" s="1"/>
     </row>
-    <row r="674" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="674" ht="12.75" customHeight="true">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -11511,7 +11933,7 @@
       <c r="M674" s="1"/>
       <c r="N674" s="1"/>
     </row>
-    <row r="675" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="675" ht="12.75" customHeight="true">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -11527,7 +11949,7 @@
       <c r="M675" s="1"/>
       <c r="N675" s="1"/>
     </row>
-    <row r="676" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="676" ht="12.75" customHeight="true">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -11543,7 +11965,7 @@
       <c r="M676" s="1"/>
       <c r="N676" s="1"/>
     </row>
-    <row r="677" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="677" ht="12.75" customHeight="true">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -11559,7 +11981,7 @@
       <c r="M677" s="1"/>
       <c r="N677" s="1"/>
     </row>
-    <row r="678" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="678" ht="12.75" customHeight="true">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -11575,7 +11997,7 @@
       <c r="M678" s="1"/>
       <c r="N678" s="1"/>
     </row>
-    <row r="679" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="679" ht="12.75" customHeight="true">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -11591,7 +12013,7 @@
       <c r="M679" s="1"/>
       <c r="N679" s="1"/>
     </row>
-    <row r="680" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="680" ht="12.75" customHeight="true">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -11607,7 +12029,7 @@
       <c r="M680" s="1"/>
       <c r="N680" s="1"/>
     </row>
-    <row r="681" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="681" ht="12.75" customHeight="true">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -11623,7 +12045,7 @@
       <c r="M681" s="1"/>
       <c r="N681" s="1"/>
     </row>
-    <row r="682" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="682" ht="12.75" customHeight="true">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -11639,7 +12061,7 @@
       <c r="M682" s="1"/>
       <c r="N682" s="1"/>
     </row>
-    <row r="683" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="683" ht="12.75" customHeight="true">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -11655,7 +12077,7 @@
       <c r="M683" s="1"/>
       <c r="N683" s="1"/>
     </row>
-    <row r="684" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="684" ht="12.75" customHeight="true">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -11671,7 +12093,7 @@
       <c r="M684" s="1"/>
       <c r="N684" s="1"/>
     </row>
-    <row r="685" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="685" ht="12.75" customHeight="true">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -11687,7 +12109,7 @@
       <c r="M685" s="1"/>
       <c r="N685" s="1"/>
     </row>
-    <row r="686" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="686" ht="12.75" customHeight="true">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -11703,7 +12125,7 @@
       <c r="M686" s="1"/>
       <c r="N686" s="1"/>
     </row>
-    <row r="687" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="687" ht="12.75" customHeight="true">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -11719,7 +12141,7 @@
       <c r="M687" s="1"/>
       <c r="N687" s="1"/>
     </row>
-    <row r="688" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="688" ht="12.75" customHeight="true">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -11735,7 +12157,7 @@
       <c r="M688" s="1"/>
       <c r="N688" s="1"/>
     </row>
-    <row r="689" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="689" ht="12.75" customHeight="true">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -11751,7 +12173,7 @@
       <c r="M689" s="1"/>
       <c r="N689" s="1"/>
     </row>
-    <row r="690" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="690" ht="12.75" customHeight="true">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -11767,7 +12189,7 @@
       <c r="M690" s="1"/>
       <c r="N690" s="1"/>
     </row>
-    <row r="691" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="691" ht="12.75" customHeight="true">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -11783,7 +12205,7 @@
       <c r="M691" s="1"/>
       <c r="N691" s="1"/>
     </row>
-    <row r="692" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="692" ht="12.75" customHeight="true">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -11799,7 +12221,7 @@
       <c r="M692" s="1"/>
       <c r="N692" s="1"/>
     </row>
-    <row r="693" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="693" ht="12.75" customHeight="true">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -11815,7 +12237,7 @@
       <c r="M693" s="1"/>
       <c r="N693" s="1"/>
     </row>
-    <row r="694" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="694" ht="12.75" customHeight="true">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -11831,7 +12253,7 @@
       <c r="M694" s="1"/>
       <c r="N694" s="1"/>
     </row>
-    <row r="695" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="695" ht="12.75" customHeight="true">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -11847,7 +12269,7 @@
       <c r="M695" s="1"/>
       <c r="N695" s="1"/>
     </row>
-    <row r="696" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="696" ht="12.75" customHeight="true">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -11863,7 +12285,7 @@
       <c r="M696" s="1"/>
       <c r="N696" s="1"/>
     </row>
-    <row r="697" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="697" ht="12.75" customHeight="true">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -11879,7 +12301,7 @@
       <c r="M697" s="1"/>
       <c r="N697" s="1"/>
     </row>
-    <row r="698" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="698" ht="12.75" customHeight="true">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -11895,7 +12317,7 @@
       <c r="M698" s="1"/>
       <c r="N698" s="1"/>
     </row>
-    <row r="699" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="699" ht="12.75" customHeight="true">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -11911,7 +12333,7 @@
       <c r="M699" s="1"/>
       <c r="N699" s="1"/>
     </row>
-    <row r="700" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="700" ht="12.75" customHeight="true">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -11927,7 +12349,7 @@
       <c r="M700" s="1"/>
       <c r="N700" s="1"/>
     </row>
-    <row r="701" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="701" ht="12.75" customHeight="true">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -11943,7 +12365,7 @@
       <c r="M701" s="1"/>
       <c r="N701" s="1"/>
     </row>
-    <row r="702" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="702" ht="12.75" customHeight="true">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -11959,7 +12381,7 @@
       <c r="M702" s="1"/>
       <c r="N702" s="1"/>
     </row>
-    <row r="703" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="703" ht="12.75" customHeight="true">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -11975,7 +12397,7 @@
       <c r="M703" s="1"/>
       <c r="N703" s="1"/>
     </row>
-    <row r="704" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="704" ht="12.75" customHeight="true">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -11991,7 +12413,7 @@
       <c r="M704" s="1"/>
       <c r="N704" s="1"/>
     </row>
-    <row r="705" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="705" ht="12.75" customHeight="true">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -12007,7 +12429,7 @@
       <c r="M705" s="1"/>
       <c r="N705" s="1"/>
     </row>
-    <row r="706" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="706" ht="12.75" customHeight="true">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -12023,7 +12445,7 @@
       <c r="M706" s="1"/>
       <c r="N706" s="1"/>
     </row>
-    <row r="707" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="707" ht="12.75" customHeight="true">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -12039,7 +12461,7 @@
       <c r="M707" s="1"/>
       <c r="N707" s="1"/>
     </row>
-    <row r="708" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="708" ht="12.75" customHeight="true">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -12055,7 +12477,7 @@
       <c r="M708" s="1"/>
       <c r="N708" s="1"/>
     </row>
-    <row r="709" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="709" ht="12.75" customHeight="true">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -12071,7 +12493,7 @@
       <c r="M709" s="1"/>
       <c r="N709" s="1"/>
     </row>
-    <row r="710" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="710" ht="12.75" customHeight="true">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -12087,7 +12509,7 @@
       <c r="M710" s="1"/>
       <c r="N710" s="1"/>
     </row>
-    <row r="711" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="711" ht="12.75" customHeight="true">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -12103,7 +12525,7 @@
       <c r="M711" s="1"/>
       <c r="N711" s="1"/>
     </row>
-    <row r="712" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="712" ht="12.75" customHeight="true">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -12119,7 +12541,7 @@
       <c r="M712" s="1"/>
       <c r="N712" s="1"/>
     </row>
-    <row r="713" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="713" ht="12.75" customHeight="true">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -12135,7 +12557,7 @@
       <c r="M713" s="1"/>
       <c r="N713" s="1"/>
     </row>
-    <row r="714" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="714" ht="12.75" customHeight="true">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -12151,7 +12573,7 @@
       <c r="M714" s="1"/>
       <c r="N714" s="1"/>
     </row>
-    <row r="715" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="715" ht="12.75" customHeight="true">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -12167,7 +12589,7 @@
       <c r="M715" s="1"/>
       <c r="N715" s="1"/>
     </row>
-    <row r="716" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="716" ht="12.75" customHeight="true">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -12183,7 +12605,7 @@
       <c r="M716" s="1"/>
       <c r="N716" s="1"/>
     </row>
-    <row r="717" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="717" ht="12.75" customHeight="true">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -12199,7 +12621,7 @@
       <c r="M717" s="1"/>
       <c r="N717" s="1"/>
     </row>
-    <row r="718" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="718" ht="12.75" customHeight="true">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -12215,7 +12637,7 @@
       <c r="M718" s="1"/>
       <c r="N718" s="1"/>
     </row>
-    <row r="719" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="719" ht="12.75" customHeight="true">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -12231,7 +12653,7 @@
       <c r="M719" s="1"/>
       <c r="N719" s="1"/>
     </row>
-    <row r="720" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="720" ht="12.75" customHeight="true">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -12247,7 +12669,7 @@
       <c r="M720" s="1"/>
       <c r="N720" s="1"/>
     </row>
-    <row r="721" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="721" ht="12.75" customHeight="true">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -12263,7 +12685,7 @@
       <c r="M721" s="1"/>
       <c r="N721" s="1"/>
     </row>
-    <row r="722" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="722" ht="12.75" customHeight="true">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -12279,7 +12701,7 @@
       <c r="M722" s="1"/>
       <c r="N722" s="1"/>
     </row>
-    <row r="723" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="723" ht="12.75" customHeight="true">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -12295,7 +12717,7 @@
       <c r="M723" s="1"/>
       <c r="N723" s="1"/>
     </row>
-    <row r="724" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="724" ht="12.75" customHeight="true">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -12311,7 +12733,7 @@
       <c r="M724" s="1"/>
       <c r="N724" s="1"/>
     </row>
-    <row r="725" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="725" ht="12.75" customHeight="true">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -12327,7 +12749,7 @@
       <c r="M725" s="1"/>
       <c r="N725" s="1"/>
     </row>
-    <row r="726" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="726" ht="12.75" customHeight="true">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -12343,7 +12765,7 @@
       <c r="M726" s="1"/>
       <c r="N726" s="1"/>
     </row>
-    <row r="727" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="727" ht="12.75" customHeight="true">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -12359,7 +12781,7 @@
       <c r="M727" s="1"/>
       <c r="N727" s="1"/>
     </row>
-    <row r="728" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="728" ht="12.75" customHeight="true">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -12375,7 +12797,7 @@
       <c r="M728" s="1"/>
       <c r="N728" s="1"/>
     </row>
-    <row r="729" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="729" ht="12.75" customHeight="true">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -12391,7 +12813,7 @@
       <c r="M729" s="1"/>
       <c r="N729" s="1"/>
     </row>
-    <row r="730" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="730" ht="12.75" customHeight="true">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -12407,7 +12829,7 @@
       <c r="M730" s="1"/>
       <c r="N730" s="1"/>
     </row>
-    <row r="731" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="731" ht="12.75" customHeight="true">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -12423,7 +12845,7 @@
       <c r="M731" s="1"/>
       <c r="N731" s="1"/>
     </row>
-    <row r="732" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="732" ht="12.75" customHeight="true">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -12439,7 +12861,7 @@
       <c r="M732" s="1"/>
       <c r="N732" s="1"/>
     </row>
-    <row r="733" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="733" ht="12.75" customHeight="true">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -12455,7 +12877,7 @@
       <c r="M733" s="1"/>
       <c r="N733" s="1"/>
     </row>
-    <row r="734" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="734" ht="12.75" customHeight="true">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -12471,7 +12893,7 @@
       <c r="M734" s="1"/>
       <c r="N734" s="1"/>
     </row>
-    <row r="735" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="735" ht="12.75" customHeight="true">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -12487,7 +12909,7 @@
       <c r="M735" s="1"/>
       <c r="N735" s="1"/>
     </row>
-    <row r="736" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="736" ht="12.75" customHeight="true">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -12503,7 +12925,7 @@
       <c r="M736" s="1"/>
       <c r="N736" s="1"/>
     </row>
-    <row r="737" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="737" ht="12.75" customHeight="true">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -12519,7 +12941,7 @@
       <c r="M737" s="1"/>
       <c r="N737" s="1"/>
     </row>
-    <row r="738" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="738" ht="12.75" customHeight="true">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -12535,7 +12957,7 @@
       <c r="M738" s="1"/>
       <c r="N738" s="1"/>
     </row>
-    <row r="739" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="739" ht="12.75" customHeight="true">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -12551,7 +12973,7 @@
       <c r="M739" s="1"/>
       <c r="N739" s="1"/>
     </row>
-    <row r="740" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="740" ht="12.75" customHeight="true">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -12567,7 +12989,7 @@
       <c r="M740" s="1"/>
       <c r="N740" s="1"/>
     </row>
-    <row r="741" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="741" ht="12.75" customHeight="true">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -12583,7 +13005,7 @@
       <c r="M741" s="1"/>
       <c r="N741" s="1"/>
     </row>
-    <row r="742" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="742" ht="12.75" customHeight="true">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -12599,7 +13021,7 @@
       <c r="M742" s="1"/>
       <c r="N742" s="1"/>
     </row>
-    <row r="743" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="743" ht="12.75" customHeight="true">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -12615,7 +13037,7 @@
       <c r="M743" s="1"/>
       <c r="N743" s="1"/>
     </row>
-    <row r="744" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="744" ht="12.75" customHeight="true">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -12631,7 +13053,7 @@
       <c r="M744" s="1"/>
       <c r="N744" s="1"/>
     </row>
-    <row r="745" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="745" ht="12.75" customHeight="true">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -12647,7 +13069,7 @@
       <c r="M745" s="1"/>
       <c r="N745" s="1"/>
     </row>
-    <row r="746" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="746" ht="12.75" customHeight="true">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -12663,7 +13085,7 @@
       <c r="M746" s="1"/>
       <c r="N746" s="1"/>
     </row>
-    <row r="747" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="747" ht="12.75" customHeight="true">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -12679,7 +13101,7 @@
       <c r="M747" s="1"/>
       <c r="N747" s="1"/>
     </row>
-    <row r="748" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="748" ht="12.75" customHeight="true">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -12695,7 +13117,7 @@
       <c r="M748" s="1"/>
       <c r="N748" s="1"/>
     </row>
-    <row r="749" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="749" ht="12.75" customHeight="true">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -12711,7 +13133,7 @@
       <c r="M749" s="1"/>
       <c r="N749" s="1"/>
     </row>
-    <row r="750" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="750" ht="12.75" customHeight="true">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -12727,7 +13149,7 @@
       <c r="M750" s="1"/>
       <c r="N750" s="1"/>
     </row>
-    <row r="751" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="751" ht="12.75" customHeight="true">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -12743,7 +13165,7 @@
       <c r="M751" s="1"/>
       <c r="N751" s="1"/>
     </row>
-    <row r="752" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="752" ht="12.75" customHeight="true">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -12759,7 +13181,7 @@
       <c r="M752" s="1"/>
       <c r="N752" s="1"/>
     </row>
-    <row r="753" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="753" ht="12.75" customHeight="true">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -12775,7 +13197,7 @@
       <c r="M753" s="1"/>
       <c r="N753" s="1"/>
     </row>
-    <row r="754" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="754" ht="12.75" customHeight="true">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -12791,7 +13213,7 @@
       <c r="M754" s="1"/>
       <c r="N754" s="1"/>
     </row>
-    <row r="755" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="755" ht="12.75" customHeight="true">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -12807,7 +13229,7 @@
       <c r="M755" s="1"/>
       <c r="N755" s="1"/>
     </row>
-    <row r="756" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="756" ht="12.75" customHeight="true">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -12823,7 +13245,7 @@
       <c r="M756" s="1"/>
       <c r="N756" s="1"/>
     </row>
-    <row r="757" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="757" ht="12.75" customHeight="true">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -12839,7 +13261,7 @@
       <c r="M757" s="1"/>
       <c r="N757" s="1"/>
     </row>
-    <row r="758" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="758" ht="12.75" customHeight="true">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -12855,7 +13277,7 @@
       <c r="M758" s="1"/>
       <c r="N758" s="1"/>
     </row>
-    <row r="759" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="759" ht="12.75" customHeight="true">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -12871,7 +13293,7 @@
       <c r="M759" s="1"/>
       <c r="N759" s="1"/>
     </row>
-    <row r="760" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="760" ht="12.75" customHeight="true">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -12887,7 +13309,7 @@
       <c r="M760" s="1"/>
       <c r="N760" s="1"/>
     </row>
-    <row r="761" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="761" ht="12.75" customHeight="true">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -12903,7 +13325,7 @@
       <c r="M761" s="1"/>
       <c r="N761" s="1"/>
     </row>
-    <row r="762" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="762" ht="12.75" customHeight="true">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -12919,7 +13341,7 @@
       <c r="M762" s="1"/>
       <c r="N762" s="1"/>
     </row>
-    <row r="763" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="763" ht="12.75" customHeight="true">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -12935,7 +13357,7 @@
       <c r="M763" s="1"/>
       <c r="N763" s="1"/>
     </row>
-    <row r="764" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="764" ht="12.75" customHeight="true">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -12951,7 +13373,7 @@
       <c r="M764" s="1"/>
       <c r="N764" s="1"/>
     </row>
-    <row r="765" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="765" ht="12.75" customHeight="true">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -12967,7 +13389,7 @@
       <c r="M765" s="1"/>
       <c r="N765" s="1"/>
     </row>
-    <row r="766" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="766" ht="12.75" customHeight="true">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -12983,7 +13405,7 @@
       <c r="M766" s="1"/>
       <c r="N766" s="1"/>
     </row>
-    <row r="767" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="767" ht="12.75" customHeight="true">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -12999,7 +13421,7 @@
       <c r="M767" s="1"/>
       <c r="N767" s="1"/>
     </row>
-    <row r="768" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="768" ht="12.75" customHeight="true">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -13015,7 +13437,7 @@
       <c r="M768" s="1"/>
       <c r="N768" s="1"/>
     </row>
-    <row r="769" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="769" ht="12.75" customHeight="true">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -13031,7 +13453,7 @@
       <c r="M769" s="1"/>
       <c r="N769" s="1"/>
     </row>
-    <row r="770" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="770" ht="12.75" customHeight="true">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -13047,7 +13469,7 @@
       <c r="M770" s="1"/>
       <c r="N770" s="1"/>
     </row>
-    <row r="771" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="771" ht="12.75" customHeight="true">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -13063,7 +13485,7 @@
       <c r="M771" s="1"/>
       <c r="N771" s="1"/>
     </row>
-    <row r="772" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="772" ht="12.75" customHeight="true">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -13079,7 +13501,7 @@
       <c r="M772" s="1"/>
       <c r="N772" s="1"/>
     </row>
-    <row r="773" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="773" ht="12.75" customHeight="true">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -13095,7 +13517,7 @@
       <c r="M773" s="1"/>
       <c r="N773" s="1"/>
     </row>
-    <row r="774" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="774" ht="12.75" customHeight="true">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -13111,7 +13533,7 @@
       <c r="M774" s="1"/>
       <c r="N774" s="1"/>
     </row>
-    <row r="775" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="775" ht="12.75" customHeight="true">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -13127,7 +13549,7 @@
       <c r="M775" s="1"/>
       <c r="N775" s="1"/>
     </row>
-    <row r="776" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="776" ht="12.75" customHeight="true">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -13143,7 +13565,7 @@
       <c r="M776" s="1"/>
       <c r="N776" s="1"/>
     </row>
-    <row r="777" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="777" ht="12.75" customHeight="true">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -13159,7 +13581,7 @@
       <c r="M777" s="1"/>
       <c r="N777" s="1"/>
     </row>
-    <row r="778" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="778" ht="12.75" customHeight="true">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -13175,7 +13597,7 @@
       <c r="M778" s="1"/>
       <c r="N778" s="1"/>
     </row>
-    <row r="779" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="779" ht="12.75" customHeight="true">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -13191,7 +13613,7 @@
       <c r="M779" s="1"/>
       <c r="N779" s="1"/>
     </row>
-    <row r="780" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="780" ht="12.75" customHeight="true">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -13207,7 +13629,7 @@
       <c r="M780" s="1"/>
       <c r="N780" s="1"/>
     </row>
-    <row r="781" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="781" ht="12.75" customHeight="true">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -13223,7 +13645,7 @@
       <c r="M781" s="1"/>
       <c r="N781" s="1"/>
     </row>
-    <row r="782" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="782" ht="12.75" customHeight="true">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -13239,7 +13661,7 @@
       <c r="M782" s="1"/>
       <c r="N782" s="1"/>
     </row>
-    <row r="783" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="783" ht="12.75" customHeight="true">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -13255,7 +13677,7 @@
       <c r="M783" s="1"/>
       <c r="N783" s="1"/>
     </row>
-    <row r="784" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="784" ht="12.75" customHeight="true">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -13271,7 +13693,7 @@
       <c r="M784" s="1"/>
       <c r="N784" s="1"/>
     </row>
-    <row r="785" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="785" ht="12.75" customHeight="true">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -13287,7 +13709,7 @@
       <c r="M785" s="1"/>
       <c r="N785" s="1"/>
     </row>
-    <row r="786" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="786" ht="12.75" customHeight="true">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -13303,7 +13725,7 @@
       <c r="M786" s="1"/>
       <c r="N786" s="1"/>
     </row>
-    <row r="787" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="787" ht="12.75" customHeight="true">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -13319,7 +13741,7 @@
       <c r="M787" s="1"/>
       <c r="N787" s="1"/>
     </row>
-    <row r="788" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="788" ht="12.75" customHeight="true">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -13335,7 +13757,7 @@
       <c r="M788" s="1"/>
       <c r="N788" s="1"/>
     </row>
-    <row r="789" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="789" ht="12.75" customHeight="true">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -13351,7 +13773,7 @@
       <c r="M789" s="1"/>
       <c r="N789" s="1"/>
     </row>
-    <row r="790" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="790" ht="12.75" customHeight="true">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -13367,7 +13789,7 @@
       <c r="M790" s="1"/>
       <c r="N790" s="1"/>
     </row>
-    <row r="791" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="791" ht="12.75" customHeight="true">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -13383,7 +13805,7 @@
       <c r="M791" s="1"/>
       <c r="N791" s="1"/>
     </row>
-    <row r="792" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="792" ht="12.75" customHeight="true">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -13399,7 +13821,7 @@
       <c r="M792" s="1"/>
       <c r="N792" s="1"/>
     </row>
-    <row r="793" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="793" ht="12.75" customHeight="true">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -13415,7 +13837,7 @@
       <c r="M793" s="1"/>
       <c r="N793" s="1"/>
     </row>
-    <row r="794" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="794" ht="12.75" customHeight="true">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -13431,7 +13853,7 @@
       <c r="M794" s="1"/>
       <c r="N794" s="1"/>
     </row>
-    <row r="795" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="795" ht="12.75" customHeight="true">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -13447,7 +13869,7 @@
       <c r="M795" s="1"/>
       <c r="N795" s="1"/>
     </row>
-    <row r="796" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="796" ht="12.75" customHeight="true">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -13463,7 +13885,7 @@
       <c r="M796" s="1"/>
       <c r="N796" s="1"/>
     </row>
-    <row r="797" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="797" ht="12.75" customHeight="true">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -13479,7 +13901,7 @@
       <c r="M797" s="1"/>
       <c r="N797" s="1"/>
     </row>
-    <row r="798" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="798" ht="12.75" customHeight="true">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -13495,7 +13917,7 @@
       <c r="M798" s="1"/>
       <c r="N798" s="1"/>
     </row>
-    <row r="799" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="799" ht="12.75" customHeight="true">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -13511,7 +13933,7 @@
       <c r="M799" s="1"/>
       <c r="N799" s="1"/>
     </row>
-    <row r="800" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="800" ht="12.75" customHeight="true">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -13527,7 +13949,7 @@
       <c r="M800" s="1"/>
       <c r="N800" s="1"/>
     </row>
-    <row r="801" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="801" ht="12.75" customHeight="true">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -13543,7 +13965,7 @@
       <c r="M801" s="1"/>
       <c r="N801" s="1"/>
     </row>
-    <row r="802" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="802" ht="12.75" customHeight="true">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -13559,7 +13981,7 @@
       <c r="M802" s="1"/>
       <c r="N802" s="1"/>
     </row>
-    <row r="803" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="803" ht="12.75" customHeight="true">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -13575,7 +13997,7 @@
       <c r="M803" s="1"/>
       <c r="N803" s="1"/>
     </row>
-    <row r="804" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="804" ht="12.75" customHeight="true">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -13591,7 +14013,7 @@
       <c r="M804" s="1"/>
       <c r="N804" s="1"/>
     </row>
-    <row r="805" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="805" ht="12.75" customHeight="true">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -13607,7 +14029,7 @@
       <c r="M805" s="1"/>
       <c r="N805" s="1"/>
     </row>
-    <row r="806" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="806" ht="12.75" customHeight="true">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -13623,7 +14045,7 @@
       <c r="M806" s="1"/>
       <c r="N806" s="1"/>
     </row>
-    <row r="807" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="807" ht="12.75" customHeight="true">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -13639,7 +14061,7 @@
       <c r="M807" s="1"/>
       <c r="N807" s="1"/>
     </row>
-    <row r="808" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="808" ht="12.75" customHeight="true">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -13655,7 +14077,7 @@
       <c r="M808" s="1"/>
       <c r="N808" s="1"/>
     </row>
-    <row r="809" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="809" ht="12.75" customHeight="true">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -13671,7 +14093,7 @@
       <c r="M809" s="1"/>
       <c r="N809" s="1"/>
     </row>
-    <row r="810" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="810" ht="12.75" customHeight="true">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -13687,7 +14109,7 @@
       <c r="M810" s="1"/>
       <c r="N810" s="1"/>
     </row>
-    <row r="811" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="811" ht="12.75" customHeight="true">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -13703,7 +14125,7 @@
       <c r="M811" s="1"/>
       <c r="N811" s="1"/>
     </row>
-    <row r="812" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="812" ht="12.75" customHeight="true">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -13719,7 +14141,7 @@
       <c r="M812" s="1"/>
       <c r="N812" s="1"/>
     </row>
-    <row r="813" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="813" ht="12.75" customHeight="true">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -13735,7 +14157,7 @@
       <c r="M813" s="1"/>
       <c r="N813" s="1"/>
     </row>
-    <row r="814" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="814" ht="12.75" customHeight="true">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -13751,7 +14173,7 @@
       <c r="M814" s="1"/>
       <c r="N814" s="1"/>
     </row>
-    <row r="815" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="815" ht="12.75" customHeight="true">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -13767,7 +14189,7 @@
       <c r="M815" s="1"/>
       <c r="N815" s="1"/>
     </row>
-    <row r="816" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="816" ht="12.75" customHeight="true">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -13783,7 +14205,7 @@
       <c r="M816" s="1"/>
       <c r="N816" s="1"/>
     </row>
-    <row r="817" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="817" ht="12.75" customHeight="true">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -13799,7 +14221,7 @@
       <c r="M817" s="1"/>
       <c r="N817" s="1"/>
     </row>
-    <row r="818" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="818" ht="12.75" customHeight="true">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -13815,7 +14237,7 @@
       <c r="M818" s="1"/>
       <c r="N818" s="1"/>
     </row>
-    <row r="819" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="819" ht="12.75" customHeight="true">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -13831,7 +14253,7 @@
       <c r="M819" s="1"/>
       <c r="N819" s="1"/>
     </row>
-    <row r="820" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="820" ht="12.75" customHeight="true">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -13847,7 +14269,7 @@
       <c r="M820" s="1"/>
       <c r="N820" s="1"/>
     </row>
-    <row r="821" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="821" ht="12.75" customHeight="true">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -13863,7 +14285,7 @@
       <c r="M821" s="1"/>
       <c r="N821" s="1"/>
     </row>
-    <row r="822" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="822" ht="12.75" customHeight="true">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -13879,7 +14301,7 @@
       <c r="M822" s="1"/>
       <c r="N822" s="1"/>
     </row>
-    <row r="823" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="823" ht="12.75" customHeight="true">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -13895,7 +14317,7 @@
       <c r="M823" s="1"/>
       <c r="N823" s="1"/>
     </row>
-    <row r="824" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="824" ht="12.75" customHeight="true">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -13911,7 +14333,7 @@
       <c r="M824" s="1"/>
       <c r="N824" s="1"/>
     </row>
-    <row r="825" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="825" ht="12.75" customHeight="true">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -13927,7 +14349,7 @@
       <c r="M825" s="1"/>
       <c r="N825" s="1"/>
     </row>
-    <row r="826" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="826" ht="12.75" customHeight="true">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -13943,7 +14365,7 @@
       <c r="M826" s="1"/>
       <c r="N826" s="1"/>
     </row>
-    <row r="827" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="827" ht="12.75" customHeight="true">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -13959,7 +14381,7 @@
       <c r="M827" s="1"/>
       <c r="N827" s="1"/>
     </row>
-    <row r="828" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="828" ht="12.75" customHeight="true">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -13975,7 +14397,7 @@
       <c r="M828" s="1"/>
       <c r="N828" s="1"/>
     </row>
-    <row r="829" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="829" ht="12.75" customHeight="true">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -13991,7 +14413,7 @@
       <c r="M829" s="1"/>
       <c r="N829" s="1"/>
     </row>
-    <row r="830" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="830" ht="12.75" customHeight="true">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -14007,7 +14429,7 @@
       <c r="M830" s="1"/>
       <c r="N830" s="1"/>
     </row>
-    <row r="831" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="831" ht="12.75" customHeight="true">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -14023,7 +14445,7 @@
       <c r="M831" s="1"/>
       <c r="N831" s="1"/>
     </row>
-    <row r="832" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="832" ht="12.75" customHeight="true">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -14039,7 +14461,7 @@
       <c r="M832" s="1"/>
       <c r="N832" s="1"/>
     </row>
-    <row r="833" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="833" ht="12.75" customHeight="true">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -14055,7 +14477,7 @@
       <c r="M833" s="1"/>
       <c r="N833" s="1"/>
     </row>
-    <row r="834" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="834" ht="12.75" customHeight="true">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -14071,7 +14493,7 @@
       <c r="M834" s="1"/>
       <c r="N834" s="1"/>
     </row>
-    <row r="835" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="835" ht="12.75" customHeight="true">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -14087,7 +14509,7 @@
       <c r="M835" s="1"/>
       <c r="N835" s="1"/>
     </row>
-    <row r="836" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="836" ht="12.75" customHeight="true">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -14103,7 +14525,7 @@
       <c r="M836" s="1"/>
       <c r="N836" s="1"/>
     </row>
-    <row r="837" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="837" ht="12.75" customHeight="true">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -14119,7 +14541,7 @@
       <c r="M837" s="1"/>
       <c r="N837" s="1"/>
     </row>
-    <row r="838" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="838" ht="12.75" customHeight="true">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -14135,7 +14557,7 @@
       <c r="M838" s="1"/>
       <c r="N838" s="1"/>
     </row>
-    <row r="839" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="839" ht="12.75" customHeight="true">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -14151,7 +14573,7 @@
       <c r="M839" s="1"/>
       <c r="N839" s="1"/>
     </row>
-    <row r="840" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="840" ht="12.75" customHeight="true">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -14167,7 +14589,7 @@
       <c r="M840" s="1"/>
       <c r="N840" s="1"/>
     </row>
-    <row r="841" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="841" ht="12.75" customHeight="true">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -14183,7 +14605,7 @@
       <c r="M841" s="1"/>
       <c r="N841" s="1"/>
     </row>
-    <row r="842" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="842" ht="12.75" customHeight="true">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -14199,7 +14621,7 @@
       <c r="M842" s="1"/>
       <c r="N842" s="1"/>
     </row>
-    <row r="843" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="843" ht="12.75" customHeight="true">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -14215,7 +14637,7 @@
       <c r="M843" s="1"/>
       <c r="N843" s="1"/>
     </row>
-    <row r="844" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="844" ht="12.75" customHeight="true">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -14231,7 +14653,7 @@
       <c r="M844" s="1"/>
       <c r="N844" s="1"/>
     </row>
-    <row r="845" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="845" ht="12.75" customHeight="true">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -14247,7 +14669,7 @@
       <c r="M845" s="1"/>
       <c r="N845" s="1"/>
     </row>
-    <row r="846" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="846" ht="12.75" customHeight="true">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -14263,7 +14685,7 @@
       <c r="M846" s="1"/>
       <c r="N846" s="1"/>
     </row>
-    <row r="847" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="847" ht="12.75" customHeight="true">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -14279,7 +14701,7 @@
       <c r="M847" s="1"/>
       <c r="N847" s="1"/>
     </row>
-    <row r="848" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="848" ht="12.75" customHeight="true">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -14295,7 +14717,7 @@
       <c r="M848" s="1"/>
       <c r="N848" s="1"/>
     </row>
-    <row r="849" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="849" ht="12.75" customHeight="true">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -14311,7 +14733,7 @@
       <c r="M849" s="1"/>
       <c r="N849" s="1"/>
     </row>
-    <row r="850" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="850" ht="12.75" customHeight="true">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -14327,7 +14749,7 @@
       <c r="M850" s="1"/>
       <c r="N850" s="1"/>
     </row>
-    <row r="851" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="851" ht="12.75" customHeight="true">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -14343,7 +14765,7 @@
       <c r="M851" s="1"/>
       <c r="N851" s="1"/>
     </row>
-    <row r="852" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="852" ht="12.75" customHeight="true">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -14359,7 +14781,7 @@
       <c r="M852" s="1"/>
       <c r="N852" s="1"/>
     </row>
-    <row r="853" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="853" ht="12.75" customHeight="true">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -14375,7 +14797,7 @@
       <c r="M853" s="1"/>
       <c r="N853" s="1"/>
     </row>
-    <row r="854" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="854" ht="12.75" customHeight="true">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -14391,7 +14813,7 @@
       <c r="M854" s="1"/>
       <c r="N854" s="1"/>
     </row>
-    <row r="855" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="855" ht="12.75" customHeight="true">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -14407,7 +14829,7 @@
       <c r="M855" s="1"/>
       <c r="N855" s="1"/>
     </row>
-    <row r="856" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="856" ht="12.75" customHeight="true">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -14423,7 +14845,7 @@
       <c r="M856" s="1"/>
       <c r="N856" s="1"/>
     </row>
-    <row r="857" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="857" ht="12.75" customHeight="true">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -14439,7 +14861,7 @@
       <c r="M857" s="1"/>
       <c r="N857" s="1"/>
     </row>
-    <row r="858" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="858" ht="12.75" customHeight="true">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -14455,7 +14877,7 @@
       <c r="M858" s="1"/>
       <c r="N858" s="1"/>
     </row>
-    <row r="859" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="859" ht="12.75" customHeight="true">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -14471,7 +14893,7 @@
       <c r="M859" s="1"/>
       <c r="N859" s="1"/>
     </row>
-    <row r="860" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="860" ht="12.75" customHeight="true">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -14487,7 +14909,7 @@
       <c r="M860" s="1"/>
       <c r="N860" s="1"/>
     </row>
-    <row r="861" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="861" ht="12.75" customHeight="true">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -14503,7 +14925,7 @@
       <c r="M861" s="1"/>
       <c r="N861" s="1"/>
     </row>
-    <row r="862" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="862" ht="12.75" customHeight="true">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -14519,7 +14941,7 @@
       <c r="M862" s="1"/>
       <c r="N862" s="1"/>
     </row>
-    <row r="863" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="863" ht="12.75" customHeight="true">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -14535,7 +14957,7 @@
       <c r="M863" s="1"/>
       <c r="N863" s="1"/>
     </row>
-    <row r="864" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="864" ht="12.75" customHeight="true">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -14551,7 +14973,7 @@
       <c r="M864" s="1"/>
       <c r="N864" s="1"/>
     </row>
-    <row r="865" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="865" ht="12.75" customHeight="true">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -14567,7 +14989,7 @@
       <c r="M865" s="1"/>
       <c r="N865" s="1"/>
     </row>
-    <row r="866" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="866" ht="12.75" customHeight="true">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -14583,7 +15005,7 @@
       <c r="M866" s="1"/>
       <c r="N866" s="1"/>
     </row>
-    <row r="867" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="867" ht="12.75" customHeight="true">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -14599,7 +15021,7 @@
       <c r="M867" s="1"/>
       <c r="N867" s="1"/>
     </row>
-    <row r="868" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="868" ht="12.75" customHeight="true">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -14615,7 +15037,7 @@
       <c r="M868" s="1"/>
       <c r="N868" s="1"/>
     </row>
-    <row r="869" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="869" ht="12.75" customHeight="true">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -14631,7 +15053,7 @@
       <c r="M869" s="1"/>
       <c r="N869" s="1"/>
     </row>
-    <row r="870" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="870" ht="12.75" customHeight="true">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -14647,7 +15069,7 @@
       <c r="M870" s="1"/>
       <c r="N870" s="1"/>
     </row>
-    <row r="871" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="871" ht="12.75" customHeight="true">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -14663,7 +15085,7 @@
       <c r="M871" s="1"/>
       <c r="N871" s="1"/>
     </row>
-    <row r="872" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="872" ht="12.75" customHeight="true">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -14679,7 +15101,7 @@
       <c r="M872" s="1"/>
       <c r="N872" s="1"/>
     </row>
-    <row r="873" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="873" ht="12.75" customHeight="true">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -14695,7 +15117,7 @@
       <c r="M873" s="1"/>
       <c r="N873" s="1"/>
     </row>
-    <row r="874" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="874" ht="12.75" customHeight="true">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -14711,7 +15133,7 @@
       <c r="M874" s="1"/>
       <c r="N874" s="1"/>
     </row>
-    <row r="875" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="875" ht="12.75" customHeight="true">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -14727,7 +15149,7 @@
       <c r="M875" s="1"/>
       <c r="N875" s="1"/>
     </row>
-    <row r="876" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="876" ht="12.75" customHeight="true">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -14743,7 +15165,7 @@
       <c r="M876" s="1"/>
       <c r="N876" s="1"/>
     </row>
-    <row r="877" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="877" ht="12.75" customHeight="true">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -14759,7 +15181,7 @@
       <c r="M877" s="1"/>
       <c r="N877" s="1"/>
     </row>
-    <row r="878" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="878" ht="12.75" customHeight="true">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -14775,7 +15197,7 @@
       <c r="M878" s="1"/>
       <c r="N878" s="1"/>
     </row>
-    <row r="879" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="879" ht="12.75" customHeight="true">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -14791,7 +15213,7 @@
       <c r="M879" s="1"/>
       <c r="N879" s="1"/>
     </row>
-    <row r="880" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="880" ht="12.75" customHeight="true">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -14807,7 +15229,7 @@
       <c r="M880" s="1"/>
       <c r="N880" s="1"/>
     </row>
-    <row r="881" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="881" ht="12.75" customHeight="true">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -14823,7 +15245,7 @@
       <c r="M881" s="1"/>
       <c r="N881" s="1"/>
     </row>
-    <row r="882" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="882" ht="12.75" customHeight="true">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -14839,7 +15261,7 @@
       <c r="M882" s="1"/>
       <c r="N882" s="1"/>
     </row>
-    <row r="883" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="883" ht="12.75" customHeight="true">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -14855,7 +15277,7 @@
       <c r="M883" s="1"/>
       <c r="N883" s="1"/>
     </row>
-    <row r="884" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="884" ht="12.75" customHeight="true">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -14871,7 +15293,7 @@
       <c r="M884" s="1"/>
       <c r="N884" s="1"/>
     </row>
-    <row r="885" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="885" ht="12.75" customHeight="true">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -14887,7 +15309,7 @@
       <c r="M885" s="1"/>
       <c r="N885" s="1"/>
     </row>
-    <row r="886" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="886" ht="12.75" customHeight="true">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -14903,7 +15325,7 @@
       <c r="M886" s="1"/>
       <c r="N886" s="1"/>
     </row>
-    <row r="887" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="887" ht="12.75" customHeight="true">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -14919,7 +15341,7 @@
       <c r="M887" s="1"/>
       <c r="N887" s="1"/>
     </row>
-    <row r="888" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="888" ht="12.75" customHeight="true">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -14935,7 +15357,7 @@
       <c r="M888" s="1"/>
       <c r="N888" s="1"/>
     </row>
-    <row r="889" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="889" ht="12.75" customHeight="true">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -14951,7 +15373,7 @@
       <c r="M889" s="1"/>
       <c r="N889" s="1"/>
     </row>
-    <row r="890" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="890" ht="12.75" customHeight="true">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -14967,7 +15389,7 @@
       <c r="M890" s="1"/>
       <c r="N890" s="1"/>
     </row>
-    <row r="891" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="891" ht="12.75" customHeight="true">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -14983,7 +15405,7 @@
       <c r="M891" s="1"/>
       <c r="N891" s="1"/>
     </row>
-    <row r="892" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="892" ht="12.75" customHeight="true">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -14999,7 +15421,7 @@
       <c r="M892" s="1"/>
       <c r="N892" s="1"/>
     </row>
-    <row r="893" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="893" ht="12.75" customHeight="true">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -15015,7 +15437,7 @@
       <c r="M893" s="1"/>
       <c r="N893" s="1"/>
     </row>
-    <row r="894" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="894" ht="12.75" customHeight="true">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -15031,7 +15453,7 @@
       <c r="M894" s="1"/>
       <c r="N894" s="1"/>
     </row>
-    <row r="895" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="895" ht="12.75" customHeight="true">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -15047,7 +15469,7 @@
       <c r="M895" s="1"/>
       <c r="N895" s="1"/>
     </row>
-    <row r="896" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="896" ht="12.75" customHeight="true">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -15063,7 +15485,7 @@
       <c r="M896" s="1"/>
       <c r="N896" s="1"/>
     </row>
-    <row r="897" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="897" ht="12.75" customHeight="true">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -15079,7 +15501,7 @@
       <c r="M897" s="1"/>
       <c r="N897" s="1"/>
     </row>
-    <row r="898" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="898" ht="12.75" customHeight="true">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -15095,7 +15517,7 @@
       <c r="M898" s="1"/>
       <c r="N898" s="1"/>
     </row>
-    <row r="899" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="899" ht="12.75" customHeight="true">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -15111,7 +15533,7 @@
       <c r="M899" s="1"/>
       <c r="N899" s="1"/>
     </row>
-    <row r="900" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="900" ht="12.75" customHeight="true">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -15127,7 +15549,7 @@
       <c r="M900" s="1"/>
       <c r="N900" s="1"/>
     </row>
-    <row r="901" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="901" ht="12.75" customHeight="true">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -15143,7 +15565,7 @@
       <c r="M901" s="1"/>
       <c r="N901" s="1"/>
     </row>
-    <row r="902" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="902" ht="12.75" customHeight="true">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -15159,7 +15581,7 @@
       <c r="M902" s="1"/>
       <c r="N902" s="1"/>
     </row>
-    <row r="903" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="903" ht="12.75" customHeight="true">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -15175,7 +15597,7 @@
       <c r="M903" s="1"/>
       <c r="N903" s="1"/>
     </row>
-    <row r="904" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="904" ht="12.75" customHeight="true">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -15191,7 +15613,7 @@
       <c r="M904" s="1"/>
       <c r="N904" s="1"/>
     </row>
-    <row r="905" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="905" ht="12.75" customHeight="true">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -15207,7 +15629,7 @@
       <c r="M905" s="1"/>
       <c r="N905" s="1"/>
     </row>
-    <row r="906" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="906" ht="12.75" customHeight="true">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -15223,7 +15645,7 @@
       <c r="M906" s="1"/>
       <c r="N906" s="1"/>
     </row>
-    <row r="907" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="907" ht="12.75" customHeight="true">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -15239,7 +15661,7 @@
       <c r="M907" s="1"/>
       <c r="N907" s="1"/>
     </row>
-    <row r="908" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="908" ht="12.75" customHeight="true">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -15255,7 +15677,7 @@
       <c r="M908" s="1"/>
       <c r="N908" s="1"/>
     </row>
-    <row r="909" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="909" ht="12.75" customHeight="true">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -15271,7 +15693,7 @@
       <c r="M909" s="1"/>
       <c r="N909" s="1"/>
     </row>
-    <row r="910" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="910" ht="12.75" customHeight="true">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -15287,7 +15709,7 @@
       <c r="M910" s="1"/>
       <c r="N910" s="1"/>
     </row>
-    <row r="911" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="911" ht="12.75" customHeight="true">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -15303,7 +15725,7 @@
       <c r="M911" s="1"/>
       <c r="N911" s="1"/>
     </row>
-    <row r="912" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="912" ht="12.75" customHeight="true">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -15319,7 +15741,7 @@
       <c r="M912" s="1"/>
       <c r="N912" s="1"/>
     </row>
-    <row r="913" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="913" ht="12.75" customHeight="true">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -15335,7 +15757,7 @@
       <c r="M913" s="1"/>
       <c r="N913" s="1"/>
     </row>
-    <row r="914" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="914" ht="12.75" customHeight="true">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -15351,7 +15773,7 @@
       <c r="M914" s="1"/>
       <c r="N914" s="1"/>
     </row>
-    <row r="915" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="915" ht="12.75" customHeight="true">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -15367,7 +15789,7 @@
       <c r="M915" s="1"/>
       <c r="N915" s="1"/>
     </row>
-    <row r="916" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="916" ht="12.75" customHeight="true">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -15383,7 +15805,7 @@
       <c r="M916" s="1"/>
       <c r="N916" s="1"/>
     </row>
-    <row r="917" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="917" ht="12.75" customHeight="true">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -15399,7 +15821,7 @@
       <c r="M917" s="1"/>
       <c r="N917" s="1"/>
     </row>
-    <row r="918" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="918" ht="12.75" customHeight="true">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -15415,7 +15837,7 @@
       <c r="M918" s="1"/>
       <c r="N918" s="1"/>
     </row>
-    <row r="919" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="919" ht="12.75" customHeight="true">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -15431,7 +15853,7 @@
       <c r="M919" s="1"/>
       <c r="N919" s="1"/>
     </row>
-    <row r="920" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="920" ht="12.75" customHeight="true">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -15447,7 +15869,7 @@
       <c r="M920" s="1"/>
       <c r="N920" s="1"/>
     </row>
-    <row r="921" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="921" ht="12.75" customHeight="true">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -15463,7 +15885,7 @@
       <c r="M921" s="1"/>
       <c r="N921" s="1"/>
     </row>
-    <row r="922" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="922" ht="12.75" customHeight="true">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -15479,7 +15901,7 @@
       <c r="M922" s="1"/>
       <c r="N922" s="1"/>
     </row>
-    <row r="923" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="923" ht="12.75" customHeight="true">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -15495,7 +15917,7 @@
       <c r="M923" s="1"/>
       <c r="N923" s="1"/>
     </row>
-    <row r="924" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="924" ht="12.75" customHeight="true">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -15511,7 +15933,7 @@
       <c r="M924" s="1"/>
       <c r="N924" s="1"/>
     </row>
-    <row r="925" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="925" ht="12.75" customHeight="true">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -15527,7 +15949,7 @@
       <c r="M925" s="1"/>
       <c r="N925" s="1"/>
     </row>
-    <row r="926" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="926" ht="12.75" customHeight="true">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -15543,7 +15965,7 @@
       <c r="M926" s="1"/>
       <c r="N926" s="1"/>
     </row>
-    <row r="927" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="927" ht="12.75" customHeight="true">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -15559,7 +15981,7 @@
       <c r="M927" s="1"/>
       <c r="N927" s="1"/>
     </row>
-    <row r="928" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="928" ht="12.75" customHeight="true">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -15575,7 +15997,7 @@
       <c r="M928" s="1"/>
       <c r="N928" s="1"/>
     </row>
-    <row r="929" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="929" ht="12.75" customHeight="true">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -15591,7 +16013,7 @@
       <c r="M929" s="1"/>
       <c r="N929" s="1"/>
     </row>
-    <row r="930" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="930" ht="12.75" customHeight="true">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -15607,7 +16029,7 @@
       <c r="M930" s="1"/>
       <c r="N930" s="1"/>
     </row>
-    <row r="931" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="931" ht="12.75" customHeight="true">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -15623,7 +16045,7 @@
       <c r="M931" s="1"/>
       <c r="N931" s="1"/>
     </row>
-    <row r="932" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="932" ht="12.75" customHeight="true">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -15639,7 +16061,7 @@
       <c r="M932" s="1"/>
       <c r="N932" s="1"/>
     </row>
-    <row r="933" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="933" ht="12.75" customHeight="true">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -15655,7 +16077,7 @@
       <c r="M933" s="1"/>
       <c r="N933" s="1"/>
     </row>
-    <row r="934" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="934" ht="12.75" customHeight="true">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -15671,7 +16093,7 @@
       <c r="M934" s="1"/>
       <c r="N934" s="1"/>
     </row>
-    <row r="935" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="935" ht="12.75" customHeight="true">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -15687,7 +16109,7 @@
       <c r="M935" s="1"/>
       <c r="N935" s="1"/>
     </row>
-    <row r="936" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="936" ht="12.75" customHeight="true">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -15703,7 +16125,7 @@
       <c r="M936" s="1"/>
       <c r="N936" s="1"/>
     </row>
-    <row r="937" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="937" ht="12.75" customHeight="true">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -15719,7 +16141,7 @@
       <c r="M937" s="1"/>
       <c r="N937" s="1"/>
     </row>
-    <row r="938" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="938" ht="12.75" customHeight="true">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -15735,7 +16157,7 @@
       <c r="M938" s="1"/>
       <c r="N938" s="1"/>
     </row>
-    <row r="939" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="939" ht="12.75" customHeight="true">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -15751,7 +16173,7 @@
       <c r="M939" s="1"/>
       <c r="N939" s="1"/>
     </row>
-    <row r="940" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="940" ht="12.75" customHeight="true">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -15767,7 +16189,7 @@
       <c r="M940" s="1"/>
       <c r="N940" s="1"/>
     </row>
-    <row r="941" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="941" ht="12.75" customHeight="true">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -15783,7 +16205,7 @@
       <c r="M941" s="1"/>
       <c r="N941" s="1"/>
     </row>
-    <row r="942" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="942" ht="12.75" customHeight="true">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -15799,7 +16221,7 @@
       <c r="M942" s="1"/>
       <c r="N942" s="1"/>
     </row>
-    <row r="943" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="943" ht="12.75" customHeight="true">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -15815,7 +16237,7 @@
       <c r="M943" s="1"/>
       <c r="N943" s="1"/>
     </row>
-    <row r="944" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="944" ht="12.75" customHeight="true">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -15831,7 +16253,7 @@
       <c r="M944" s="1"/>
       <c r="N944" s="1"/>
     </row>
-    <row r="945" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="945" ht="12.75" customHeight="true">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -15847,7 +16269,7 @@
       <c r="M945" s="1"/>
       <c r="N945" s="1"/>
     </row>
-    <row r="946" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="946" ht="12.75" customHeight="true">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -15863,7 +16285,7 @@
       <c r="M946" s="1"/>
       <c r="N946" s="1"/>
     </row>
-    <row r="947" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="947" ht="12.75" customHeight="true">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -15879,7 +16301,7 @@
       <c r="M947" s="1"/>
       <c r="N947" s="1"/>
     </row>
-    <row r="948" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="948" ht="12.75" customHeight="true">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -15895,7 +16317,7 @@
       <c r="M948" s="1"/>
       <c r="N948" s="1"/>
     </row>
-    <row r="949" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="949" ht="12.75" customHeight="true">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -15911,7 +16333,7 @@
       <c r="M949" s="1"/>
       <c r="N949" s="1"/>
     </row>
-    <row r="950" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="950" ht="12.75" customHeight="true">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -15927,7 +16349,7 @@
       <c r="M950" s="1"/>
       <c r="N950" s="1"/>
     </row>
-    <row r="951" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="951" ht="12.75" customHeight="true">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -15943,7 +16365,7 @@
       <c r="M951" s="1"/>
       <c r="N951" s="1"/>
     </row>
-    <row r="952" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="952" ht="12.75" customHeight="true">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -15959,7 +16381,7 @@
       <c r="M952" s="1"/>
       <c r="N952" s="1"/>
     </row>
-    <row r="953" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="953" ht="12.75" customHeight="true">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -15975,7 +16397,7 @@
       <c r="M953" s="1"/>
       <c r="N953" s="1"/>
     </row>
-    <row r="954" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="954" ht="12.75" customHeight="true">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -15991,7 +16413,7 @@
       <c r="M954" s="1"/>
       <c r="N954" s="1"/>
     </row>
-    <row r="955" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="955" ht="12.75" customHeight="true">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -16007,7 +16429,7 @@
       <c r="M955" s="1"/>
       <c r="N955" s="1"/>
     </row>
-    <row r="956" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="956" ht="12.75" customHeight="true">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -16023,7 +16445,7 @@
       <c r="M956" s="1"/>
       <c r="N956" s="1"/>
     </row>
-    <row r="957" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="957" ht="12.75" customHeight="true">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -16039,7 +16461,7 @@
       <c r="M957" s="1"/>
       <c r="N957" s="1"/>
     </row>
-    <row r="958" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="958" ht="12.75" customHeight="true">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -16055,7 +16477,7 @@
       <c r="M958" s="1"/>
       <c r="N958" s="1"/>
     </row>
-    <row r="959" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="959" ht="12.75" customHeight="true">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -16071,7 +16493,7 @@
       <c r="M959" s="1"/>
       <c r="N959" s="1"/>
     </row>
-    <row r="960" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="960" ht="12.75" customHeight="true">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -16087,7 +16509,7 @@
       <c r="M960" s="1"/>
       <c r="N960" s="1"/>
     </row>
-    <row r="961" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="961" ht="12.75" customHeight="true">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -16103,7 +16525,7 @@
       <c r="M961" s="1"/>
       <c r="N961" s="1"/>
     </row>
-    <row r="962" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="962" ht="12.75" customHeight="true">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -16119,7 +16541,7 @@
       <c r="M962" s="1"/>
       <c r="N962" s="1"/>
     </row>
-    <row r="963" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="963" ht="12.75" customHeight="true">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -16135,7 +16557,7 @@
       <c r="M963" s="1"/>
       <c r="N963" s="1"/>
     </row>
-    <row r="964" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="964" ht="12.75" customHeight="true">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -16151,7 +16573,7 @@
       <c r="M964" s="1"/>
       <c r="N964" s="1"/>
     </row>
-    <row r="965" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="965" ht="12.75" customHeight="true">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -16167,7 +16589,7 @@
       <c r="M965" s="1"/>
       <c r="N965" s="1"/>
     </row>
-    <row r="966" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="966" ht="12.75" customHeight="true">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -16183,7 +16605,7 @@
       <c r="M966" s="1"/>
       <c r="N966" s="1"/>
     </row>
-    <row r="967" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="967" ht="12.75" customHeight="true">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -16199,7 +16621,7 @@
       <c r="M967" s="1"/>
       <c r="N967" s="1"/>
     </row>
-    <row r="968" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="968" ht="12.75" customHeight="true">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -16215,7 +16637,7 @@
       <c r="M968" s="1"/>
       <c r="N968" s="1"/>
     </row>
-    <row r="969" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="969" ht="12.75" customHeight="true">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -16231,7 +16653,7 @@
       <c r="M969" s="1"/>
       <c r="N969" s="1"/>
     </row>
-    <row r="970" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="970" ht="12.75" customHeight="true">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -16247,7 +16669,7 @@
       <c r="M970" s="1"/>
       <c r="N970" s="1"/>
     </row>
-    <row r="971" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="971" ht="12.75" customHeight="true">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -16263,7 +16685,7 @@
       <c r="M971" s="1"/>
       <c r="N971" s="1"/>
     </row>
-    <row r="972" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="972" ht="12.75" customHeight="true">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -16279,7 +16701,7 @@
       <c r="M972" s="1"/>
       <c r="N972" s="1"/>
     </row>
-    <row r="973" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="973" ht="12.75" customHeight="true">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -16295,7 +16717,7 @@
       <c r="M973" s="1"/>
       <c r="N973" s="1"/>
     </row>
-    <row r="974" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="974" ht="12.75" customHeight="true">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -16311,7 +16733,7 @@
       <c r="M974" s="1"/>
       <c r="N974" s="1"/>
     </row>
-    <row r="975" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="975" ht="12.75" customHeight="true">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -16327,7 +16749,7 @@
       <c r="M975" s="1"/>
       <c r="N975" s="1"/>
     </row>
-    <row r="976" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="976" ht="12.75" customHeight="true">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -16343,7 +16765,7 @@
       <c r="M976" s="1"/>
       <c r="N976" s="1"/>
     </row>
-    <row r="977" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="977" ht="12.75" customHeight="true">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -16359,7 +16781,7 @@
       <c r="M977" s="1"/>
       <c r="N977" s="1"/>
     </row>
-    <row r="978" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="978" ht="12.75" customHeight="true">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -16375,7 +16797,7 @@
       <c r="M978" s="1"/>
       <c r="N978" s="1"/>
     </row>
-    <row r="979" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="979" ht="12.75" customHeight="true">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -16391,7 +16813,7 @@
       <c r="M979" s="1"/>
       <c r="N979" s="1"/>
     </row>
-    <row r="980" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="980" ht="12.75" customHeight="true">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -16407,7 +16829,7 @@
       <c r="M980" s="1"/>
       <c r="N980" s="1"/>
     </row>
-    <row r="981" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="981" ht="12.75" customHeight="true">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -16423,7 +16845,7 @@
       <c r="M981" s="1"/>
       <c r="N981" s="1"/>
     </row>
-    <row r="982" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="982" ht="12.75" customHeight="true">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -16439,7 +16861,7 @@
       <c r="M982" s="1"/>
       <c r="N982" s="1"/>
     </row>
-    <row r="983" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="983" ht="12.75" customHeight="true">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -16455,7 +16877,7 @@
       <c r="M983" s="1"/>
       <c r="N983" s="1"/>
     </row>
-    <row r="984" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="984" ht="12.75" customHeight="true">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -16471,7 +16893,7 @@
       <c r="M984" s="1"/>
       <c r="N984" s="1"/>
     </row>
-    <row r="985" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="985" ht="12.75" customHeight="true">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -16487,7 +16909,7 @@
       <c r="M985" s="1"/>
       <c r="N985" s="1"/>
     </row>
-    <row r="986" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="986" ht="12.75" customHeight="true">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -16503,7 +16925,7 @@
       <c r="M986" s="1"/>
       <c r="N986" s="1"/>
     </row>
-    <row r="987" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="987" ht="12.75" customHeight="true">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -16519,7 +16941,7 @@
       <c r="M987" s="1"/>
       <c r="N987" s="1"/>
     </row>
-    <row r="988" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="988" ht="12.75" customHeight="true">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -16535,7 +16957,7 @@
       <c r="M988" s="1"/>
       <c r="N988" s="1"/>
     </row>
-    <row r="989" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="989" ht="12.75" customHeight="true">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -16551,7 +16973,7 @@
       <c r="M989" s="1"/>
       <c r="N989" s="1"/>
     </row>
-    <row r="990" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="990" ht="12.75" customHeight="true">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -16567,7 +16989,7 @@
       <c r="M990" s="1"/>
       <c r="N990" s="1"/>
     </row>
-    <row r="991" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="991" ht="12.75" customHeight="true">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -16583,7 +17005,7 @@
       <c r="M991" s="1"/>
       <c r="N991" s="1"/>
     </row>
-    <row r="992" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="992" ht="12.75" customHeight="true">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -16599,7 +17021,7 @@
       <c r="M992" s="1"/>
       <c r="N992" s="1"/>
     </row>
-    <row r="993" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="993" ht="12.75" customHeight="true">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -16615,7 +17037,7 @@
       <c r="M993" s="1"/>
       <c r="N993" s="1"/>
     </row>
-    <row r="994" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="994" ht="12.75" customHeight="true">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -16631,7 +17053,7 @@
       <c r="M994" s="1"/>
       <c r="N994" s="1"/>
     </row>
-    <row r="995" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="995" ht="12.75" customHeight="true">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -16647,7 +17069,7 @@
       <c r="M995" s="1"/>
       <c r="N995" s="1"/>
     </row>
-    <row r="996" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="996" ht="12.75" customHeight="true">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -16663,7 +17085,7 @@
       <c r="M996" s="1"/>
       <c r="N996" s="1"/>
     </row>
-    <row r="997" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="997" ht="12.75" customHeight="true">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -16679,7 +17101,7 @@
       <c r="M997" s="1"/>
       <c r="N997" s="1"/>
     </row>
-    <row r="998" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="998" ht="12.75" customHeight="true">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -16695,7 +17117,7 @@
       <c r="M998" s="1"/>
       <c r="N998" s="1"/>
     </row>
-    <row r="999" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="999" ht="12.75" customHeight="true">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -16711,7 +17133,7 @@
       <c r="M999" s="1"/>
       <c r="N999" s="1"/>
     </row>
-    <row r="1000" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1000" ht="12.75" customHeight="true">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -16747,11 +17169,9 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
   </mergeCells>
-  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;A</oddHeader>
-    <oddFooter>&amp;CPágina &amp;P</oddFooter>
-  </headerFooter>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <headerFooter alignWithMargins="1"/>
 </worksheet>
 </file>